--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -735,34 +735,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n"/>
+      <c r="C4" s="3" t="n">
+        <v>289.1</v>
+      </c>
       <c r="D4" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>16</v>
+        <v>22.9</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>451.2</v>
+        <v>411.2</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18</v>
@@ -771,7 +771,7 @@
         <v>99.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0.1</v>
@@ -783,16 +783,16 @@
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>4.3</v>
+        <v>13.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
@@ -801,7 +801,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -816,12 +816,14 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>464.5</v>
+      </c>
       <c r="D5" s="3" t="n">
         <v>265.1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>20.3</v>
@@ -842,29 +844,33 @@
         <v>0.1</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>19</v>
+        <v>14.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n">
-        <v>2.5</v>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+990
+</t>
+        </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>18.9</v>
+        <v>22.3</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>90.5</v>
+        <v>26.5</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>4.8</v>
@@ -879,10 +885,10 @@
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -898,10 +904,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>338</v>
+        <v>38.9</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>14.3</v>
@@ -909,42 +915,40 @@
       <c r="F6" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="G6" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>26.1</v>
+        <v>94.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>62.5</v>
@@ -953,19 +957,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20.2</v>
+        <v>21.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>93</v>
+        <v>931</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -981,7 +985,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
+        <v>355.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>25.3</v>
@@ -992,63 +996,65 @@
       <c r="F7" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="I7" s="3" t="n"/>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>27.1</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>2.7</v>
+        <v>0.2</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>4.8</v>
+        <v>34.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>24.4</v>
+        <v>1.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>67.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>1.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X7" s="8" t="n">
-        <v>81.3</v>
+      <c r="W7" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1070,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>327.9</v>
+        <v>7.2</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
@@ -1073,36 +1079,36 @@
         <v>14.8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>19.9</v>
+        <v>29.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>13.1</v>
+        <v>5.2</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>5.1</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>318.9</v>
+        <v>2721.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P8" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1111,10 +1117,10 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.8</v>
@@ -1122,14 +1128,14 @@
       <c r="W8" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>19.2</v>
+      <c r="X8" s="8" t="n">
+        <v>92.8</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>83</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1146,7 +1152,7 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n">
-        <v>16.5</v>
+        <v>26.5</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>7.4</v>
@@ -1155,37 +1161,41 @@
         <v>19.6</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>14.2</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.5</v>
+        <v>134.2</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>61.6</v>
+        <v>0.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1128.9</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>284.4</v>
+      </c>
       <c r="L9" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="N9" s="3" t="n"/>
+        <v>45.1</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>108.2</v>
+        <v>29.8</v>
       </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
         <v>103.3</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>892.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>5.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>393.1</v>
@@ -1198,13 +1208,13 @@
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>94.8</v>
+        <v>34.8</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1219,29 +1229,27 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>156.3</v>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n">
-        <v>165.1</v>
+        <v>26.5</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14.3</v>
+        <v>0.6</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9.9</v>
+        <v>33</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>55</v>
+        <v>17.7</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>61.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n">
@@ -1250,42 +1258,44 @@
       <c r="M10" s="3" t="n">
         <v>74.3</v>
       </c>
-      <c r="N10" s="3" t="n"/>
+      <c r="N10" s="8" t="n">
+        <v>637.9</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>118.6</v>
+        <v>43</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>20.7</v>
+        <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>44.1</v>
+        <v>1.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>91.40000000000001</v>
+        <v>54.1</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>19</v>
+        <v>7.9</v>
+      </c>
+      <c r="X10" s="8" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1301,31 +1311,39 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="D11" s="3" t="n"/>
+        <v>7787.1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>197.5</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n">
-        <v>1.7</v>
+        <v>13.3</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
+        <v>1.3</v>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>23.8</v>
+      </c>
       <c r="M11" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="N11" s="3" t="n"/>
+      <c r="N11" s="3" t="n">
+        <v>15.6</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -1333,33 +1351,35 @@
         <v>1.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>81.7</v>
+        <v>221.3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>89.5</v>
+        <v>19.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>18.6</v>
+      <c r="V11" s="3" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>18.9</v>
+        <v>484.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>20.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+        <v>15.1</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1377,49 +1397,51 @@
         <v>23.4</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>13.9</v>
+        <v>23.3</v>
       </c>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>10</v>
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>0.4</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277275
+163
+</t>
+        </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <v>17.9</v>
+      <c r="R12" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>14.9</v>
+        <v>1.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>858.9</v>
+        <v>18.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1428,16 +1450,16 @@
         <v>21.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.3</v>
+        <v>1.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>88</v>
+        <v>885</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>93.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1453,61 +1475,59 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>51.7</v>
+        <v>24.6</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>25.7</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.1</v>
+        <v>11.5</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>13</v>
+        <v>23.9</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>82.2</v>
+        <v>2.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>11.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>4.4</v>
+        <v>44.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P13" s="3" t="n"/>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="S13" s="3" t="n">
         <v>19.2</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>66.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>39.8</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
@@ -1516,12 +1536,14 @@
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>26.8</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1537,44 +1559,46 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n">
-        <v>24.6</v>
+        <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2.3</v>
+        <v>23.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>114.4</v>
+        <v>444.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>2.8</v>
+      <c r="J14" s="8" t="n">
+        <v>56.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.4</v>
+        <v>9.9</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="O14" s="3" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>997.9</v>
+      </c>
       <c r="P14" s="3" t="n">
-        <v>0.8</v>
+        <v>18.5</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>18.8</v>
@@ -1583,25 +1607,25 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>20.6</v>
+        <v>2.8</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>6.5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1618,42 +1642,42 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>19.1</v>
+        <v>26.7</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>10.7</v>
+        <v>16.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1</v>
+        <v>8.9</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="J15" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="J15" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>8488.299999999999</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>92</v>
+        <v>922.6</v>
       </c>
       <c r="P15" s="3" t="n"/>
       <c r="Q15" s="3" t="n">
-        <v>23.9</v>
+        <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1662,19 +1686,19 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>27.2</v>
+        <v>13.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>84.8</v>
@@ -1695,73 +1719,73 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="C16" s="3" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
-        <v>14.9</v>
+        <v>14.2</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>23.6</v>
+        <v>423.6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>481.9</v>
+        <v>0.7</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>21.4</v>
+        <v>2.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>4.1</v>
-      </c>
+        <v>46.9</v>
+      </c>
+      <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n">
-        <v>10.9</v>
+        <v>18.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>92.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>6.2</v>
+      </c>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>18.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>941.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>42</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
+        <v>55.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>4094.8</v>
+        <v>100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>93.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>41.1</v>
+        <v>410.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1778,73 +1802,69 @@
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="8" t="n">
-        <v>172.1</v>
+        <v>57.9</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>65.3</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>19.1</v>
+        <v>2.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>9.800000000000001</v>
+      <c r="H17" s="8" t="n">
+        <v>89.09999999999999</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>66.2</v>
+        <v>6.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.3</v>
+        <v>22.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>438.1</v>
+      </c>
+      <c r="P17" s="3" t="n"/>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>46.1</v>
+        <v>43.1</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>20.1</v>
+        <v>313</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>444.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="8" t="n">
-        <v>190.9</v>
+      <c r="X17" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>81.7</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1863,69 +1883,67 @@
       <c r="D18" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>12.6</v>
-      </c>
       <c r="I18" s="3" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.1</v>
+        <v>28.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>998.6</v>
+        <v>28.6</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>20.1</v>
+        <v>10.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>742</v>
+        <v>62.6</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="n">
-        <v>16.7</v>
+        <v>76.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>15.1</v>
+        <v>22.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>63.2</v>
+        <v>634088</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1940,60 +1958,69 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="n">
-        <v>1425.1</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>13</v>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>19.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
+        <v>0.4</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>27.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>11.4</v>
+        <v>13.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>56.1</v>
+        <v>74</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>84.8</v>
+        <v>24.9</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2015,20 +2042,18 @@
       <c r="D20" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.3</v>
@@ -2037,46 +2062,44 @@
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.8</v>
+        <v>23.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1</v>
+        <v>15.5</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>96.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>231.4</v>
+        <v>221.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>115.1</v>
+        <v>13.1</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>28.8</v>
+        <v>5.1</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>91.2</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="V20" s="3" t="n"/>
       <c r="W20" s="3" t="n">
-        <v>42.2</v>
+        <v>43.2</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.4</v>
+        <v>12.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>22.9</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.9</v>
@@ -2096,71 +2119,71 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E21" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>14</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10.8</v>
+        <v>18.8</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>21.1</v>
+        <v>2.2</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>12.6</v>
+        <v>16.5</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>88</v>
+        <v>28.8</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>29.4</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>16.6</v>
+        <v>4.2</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98</v>
+        <v>21.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2177,42 +2200,42 @@
       </c>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
+        <v>19.6</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>2.9</v>
+        <v>22.2</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L22" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M22" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>16.3</v>
-      </c>
       <c r="N22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1188.8</v>
-      </c>
-      <c r="P22" s="3" t="n"/>
+        <v>106</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="Q22" s="3" t="n">
         <v>24.6</v>
       </c>
@@ -2220,28 +2243,28 @@
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>161.8</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2263,16 +2286,16 @@
         <v>25.8</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>61.4</v>
+        <v>6.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>53.9</v>
+        <v>16.6</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>2.5</v>
@@ -2284,30 +2307,32 @@
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="M23" s="3" t="n"/>
+        <v>2.2</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="N23" s="3" t="n">
-        <v>0.8</v>
+        <v>14.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>970</v>
+        <v>4.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.1</v>
+        <v>6.6</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>115.6</v>
+        <v>1.5</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>91.5</v>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>219.8</v>
+        <v>49.2</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
@@ -2316,13 +2341,13 @@
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2337,69 +2362,69 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="8" t="n">
+      <c r="C24" s="3" t="n">
         <v>25.6</v>
       </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>97.5</v>
+        <v>7.5</v>
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n">
-        <v>10.8</v>
+        <v>53.1</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>1.7</v>
+      <c r="L24" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>21.2</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>18.9</v>
+        <v>0.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>328.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>17.3</v>
+        <v>89.09999999999999</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>17.8</v>
+        <v>30040.7</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>85.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2415,74 +2440,62 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
+        <v>37.2</v>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
-        <v>1.4</v>
+        <v>14.7</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 8
+      <c r="N25" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="3" t="n"/>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4158
+41419
 </t>
         </is>
       </c>
-      <c r="O25" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>1156.1</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="X25" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y25" s="3" t="n"/>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2496,72 +2509,76 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>19.3</v>
+        <v>0.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I26" s="3" t="n"/>
+        <v>12.6</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="J26" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n">
-        <v>16</v>
+        <v>16.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>0.1</v>
+        <v>15.3</v>
+      </c>
+      <c r="N26" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2577,69 +2594,71 @@
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G27" s="3" t="n"/>
+        <v>19.3</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>37.9</v>
+      </c>
       <c r="H27" s="3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P27" s="8" t="n">
-        <v>12.8</v>
+      <c r="N27" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.8</v>
+        <v>12.2</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>19.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87</v>
+        <v>3.9</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>19</v>
+        <v>15.6</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>17.6</v>
+        <v>15.3</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>21.8</v>
+        <v>9.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2654,71 +2673,71 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="D28" s="3" t="n">
-        <v>23.7</v>
+        <v>24.5</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.3</v>
+        <v>15.3</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n">
-        <v>11.6</v>
+        <v>13.2</v>
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N28" s="3" t="n"/>
+        <v>14.3</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>161</v>
+      </c>
       <c r="O28" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>936</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="S28" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>17.2</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>99.8</v>
+        <v>19.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2735,71 +2754,73 @@
       </c>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>81.7</v>
+        <v>3.8</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>9.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+        <v>91.2</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.6</v>
+        <v>32.8</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>44.3</v>
+        <v>5.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>28.6</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>434.3</v>
+        <v>424.1</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>19.9</v>
+        <v>17</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>31</v>
+        <v>17.2</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.6</v>
+        <v>88</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2815,72 +2836,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1116.8</v>
-      </c>
-      <c r="D30" s="3" t="n"/>
+        <v>116.8</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>23.7</v>
+      </c>
       <c r="E30" s="3" t="n">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45.9</v>
+        <v>4.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.2</v>
+        <v>24.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K30" s="3" t="n"/>
+      <c r="K30" s="3" t="n">
+        <v>6.6</v>
+      </c>
       <c r="L30" s="3" t="n">
-        <v>13.7</v>
+        <v>24.9</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>115</v>
+        <v>3.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>10.8</v>
+        <v>2.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>199.8</v>
+        <v>92</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0.2</v>
+        <v>61.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>89.2</v>
+        <v>19</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4213.8</v>
+        <v>66.7</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1.3</v>
+        <v>12.4</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>4250.1</v>
+        <v>22.1</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2896,70 +2921,82 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="D31" s="3" t="n"/>
+        <v>23.9</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
+      </c>
       <c r="E31" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>29.1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>14.3</v>
+        <v>94.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>62.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>15</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>74.3</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>9992.1</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>89.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>413.2</v>
+      </c>
       <c r="U31" s="3" t="n">
-        <v>11.4</v>
+        <v>41.5</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>63.5</v>
+        <v>85.2</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>82.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>1.5</v>
+        <v>4222.1</v>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81911955
+111
+</t>
+        </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2975,22 +3012,19 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>364.6</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144 1
-</t>
-        </is>
+      <c r="E32" s="3" t="n">
+        <v>44.1</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>12.5</v>
@@ -2998,56 +3032,61 @@
       <c r="I32" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>15</v>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>180.9</v>
+        <v>200.7</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>19.9</v>
+        <v>11.1</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>99</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.6</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 1 6
+</t>
+        </is>
       </c>
       <c r="T32" s="3" t="n">
-        <v>9</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 84
+        <v>4.4</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
 </t>
         </is>
       </c>
+      <c r="W32" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -3065,72 +3104,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>440.2</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>813.3</v>
+        <v>14.3</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>181.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="J33" s="3" t="n"/>
+      <c r="J33" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K33" s="3" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>11.6</v>
+        <v>24.3</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
+        <v>14.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>17.8</v>
+        <v>26.6</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>6.5</v>
+        <v>0.2</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>23.4</v>
+        <v>12.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.9</v>
+        <v>96</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>89.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3145,69 +3186,75 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="n">
-        <v>19.7</v>
+      <c r="C34" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>81.7</v>
+      <c r="F34" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10</v>
+        <v>102.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="I34" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="O34" s="3" t="n"/>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>29</v>
+      </c>
       <c r="P34" s="3" t="n">
-        <v>10.6</v>
+        <v>6.6</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="R34" s="3" t="n"/>
+      <c r="R34" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="S34" s="3" t="n">
-        <v>17.3</v>
+        <v>19.6</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96.8</v>
+        <v>77.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>52.2</v>
+        <v>6.5</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3222,73 +3269,75 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="D35" s="3" t="n">
-        <v>41.6</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>14.2</v>
+        <v>7.4</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M35" s="3" t="n"/>
+        <v>5.5</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>45.2</v>
+      </c>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>0.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q35" s="8" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="Q35" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n">
-        <v>15.9</v>
+        <v>12.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60</v>
+        <v>986.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>11.8</v>
+        <v>2.9</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>26.4</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>522.2</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>218.6</v>
+        <v>38.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3305,71 +3354,73 @@
       </c>
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="n">
-        <v>24.2</v>
+        <v>25.1</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>12.1</v>
+        <v>1.1</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>22.7</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>0</v>
+      <c r="H36" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="n">
-        <v>66.40000000000001</v>
+        <v>75.90000000000001</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>292</v>
+        <v>1.8</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>28.9</v>
+        <v>23.9</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.4</v>
+        <v>18.3</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
+        <v>11.8</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>20.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3386,69 +3437,83 @@
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n">
-        <v>22.3</v>
+        <v>4.5</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>19.5</v>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422112
+214101
+</t>
+        </is>
       </c>
       <c r="G37" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="H37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455266
+72
+45
+61194929
+</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.1</v>
+        <v>4.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>115</v>
+        <v>52.5</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>987.8</v>
+        <v>97.8</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>59</v>
+        <v>24.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3819.1</v>
+        <v>219.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V37" s="3" t="n"/>
+        <v>2.4</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="W37" s="3" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.5</v>
+        <v>422.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>13.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3463,69 +3528,73 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="D38" s="8" t="n">
         <v>484.1</v>
       </c>
-      <c r="E38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="F38" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="G38" s="3" t="n"/>
+        <v>32.2</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H38" s="3" t="n">
-        <v>56.9</v>
+        <v>5.7</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n">
-        <v>5</v>
+        <v>50.1</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>67.59999999999999</v>
-      </c>
+        <v>137.2</v>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n">
-        <v>26.8</v>
+        <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q38" s="8" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>380.9</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>18</v>
-      </c>
-      <c r="R38" s="3" t="n"/>
-      <c r="S38" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>90</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>126.1</v>
+        <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>185.9</v>
+        <v>15.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>8.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3541,9 +3610,9 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="D39" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="E39" s="3" t="n">
@@ -3553,62 +3622,64 @@
         <v>18.4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11.3</v>
+        <v>2.3</v>
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>13.7</v>
+        <v>82</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+141
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>8.4</v>
+        <v>38.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15.6</v>
+        <v>12.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>96</v>
+        <v>7.4</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>81</v>
+        <v>66.09999999999999</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>0.8</v>
+        <v>16.3</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y39" s="3" t="n">
-        <v>67</v>
-      </c>
+      <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3623,75 +3694,79 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>637.7</v>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+6443
+</t>
+        </is>
       </c>
       <c r="D40" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>85.09999999999999</v>
+      <c r="E40" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>3.5</v>
-      </c>
+        <v>7.8</v>
+      </c>
+      <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>41.3</v>
+        <v>1.3</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>72.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>92.2</v>
+        <v>12</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P40" s="3" t="n"/>
+        <v>99.8</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q40" s="3" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>1</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>85.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>6</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>16.7</v>
+        <v>13.8</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>116.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3706,14 +3781,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>408.8</v>
-      </c>
+      <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>159.7</v>
+      <c r="E41" s="3" t="n">
+        <v>39.7</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>17.9</v>
@@ -3722,46 +3795,44 @@
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>1.3</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="M41" s="3" t="n"/>
       <c r="N41" s="3" t="n">
-        <v>12</v>
+        <v>16.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>1</v>
+      <c r="R41" s="8" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.9</v>
+        <v>18.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>48.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>21.7</v>
@@ -3769,14 +3840,14 @@
       <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>15.8</v>
+      <c r="X41" s="8" t="n">
+        <v>85.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39.8</v>
+        <v>9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3792,10 +3863,10 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>609.4</v>
+        <v>608.8</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>11.7</v>
+        <v>26.2</v>
       </c>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
@@ -3804,26 +3875,24 @@
       <c r="G42" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n">
-        <v>4.1</v>
+        <v>47.2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>12.3</v>
+        <v>10.2</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>98</v>
@@ -3832,34 +3901,30 @@
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>8.9</v>
-      </c>
+        <v>25.6</v>
+      </c>
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="n">
-        <v>49.8</v>
+        <v>48</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>162.8</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3875,79 +3940,70 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.5</v>
+        <v>6094.4</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111416 1
-</t>
-        </is>
+        <v>26.9</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>3.5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="n"/>
       <c r="J43" s="3" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
+      </c>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>28.6</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>24.8</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S43" s="8" t="n">
-        <v>61.8</v>
+        <v>18.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>0.6</v>
+        <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>59.8</v>
+        <v>53.2</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3962,26 +4018,25 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>3119.5</v>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
+2722208602828
+</t>
+        </is>
       </c>
       <c r="D44" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="E44" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F44" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111416 1
-</t>
-        </is>
+      <c r="E44" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>3.5</v>
@@ -3989,54 +4044,46 @@
       <c r="J44" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>5002</v>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>12.2</v>
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>10110110.1</v>
+        <v>92</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S44" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>150115100011.5</v>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v>1989.8</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24222
+7
+</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>42.2</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4054,40 +4101,40 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>31.3</v>
+        <v>67272.7</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>53.4</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>92.5</v>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+24222
+</t>
+        </is>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>27.2</v>
-      </c>
+        <v>18.9</v>
+      </c>
+      <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>53.1</v>
-      </c>
+        <v>602.2</v>
+      </c>
+      <c r="M45" s="3" t="n"/>
       <c r="N45" s="3" t="n">
-        <v>621.9</v>
+        <v>6197.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>498</v>
+        <v>624.2</v>
       </c>
       <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
@@ -4097,28 +4144,28 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>827.2</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2929.8</v>
+        <v>218.1</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>29.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>108.9</v>
+        <v>1208.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>328.8</v>
+        <v>37.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4134,16 +4181,16 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>223.9</v>
+        <v>23.9</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>26.2</v>
+        <v>32.1</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>23.1</v>
+        <v>10.7</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>18.5</v>
+        <v>92.5</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>15.5</v>
@@ -4151,56 +4198,50 @@
       <c r="H46" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="I46" s="3" t="n">
-        <v>3.8</v>
+      <c r="I46" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>11.1</v>
+        <v>27.2</v>
+      </c>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>55.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="P46" s="8" t="n">
-        <v>4.4</v>
+        <v>49</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.8</v>
+        <v>89.2</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.3</v>
+        <v>26.3</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>68.40000000000001</v>
+        <v>8.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>88.09999999999999</v>
-      </c>
+        <v>2918</v>
+      </c>
+      <c r="W46" s="3" t="n"/>
+      <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="n">
-        <v>21.2</v>
+        <v>1.2</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -738,70 +738,70 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>13.8</v>
+      <c r="E4" s="8" t="n">
+        <v>113.8</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G4" s="3" t="n"/>
+        <v>19.9</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J4" s="3" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>18.9</v>
+        <v>27.8</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>411.2</v>
+        <v>13.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>266.8</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3.3</v>
+        <v>21.1</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>12.5</v>
+        <v>43.2</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -817,60 +817,56 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>464.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>265.1</v>
+        <v>1564.3</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>24</v>
+        <v>0.1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>14.9</v>
+      <c r="L5" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="N5" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>83.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>26.5</v>
+        <v>20.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>4.8</v>
@@ -878,17 +874,17 @@
       <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>76</v>
+        <v>293</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -904,72 +900,74 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
+      <c r="G6" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1141.6</v>
+      </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>17.2</v>
+        <v>1.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="M6" s="8" t="n">
+        <v>994.2</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>17.9</v>
+        <v>1.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.1</v>
+        <v>44.4</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>671.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>21.6</v>
+        <v>18.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>931</v>
+        <v>193</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.2</v>
+        <v>1103.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -985,76 +983,70 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355.2</v>
+        <v>355.7</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>10.7</v>
+      <c r="G7" s="8" t="n">
+        <v>80.09999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>27.1</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>34.8</v>
+        <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.4</v>
+        <v>41.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>77.09999999999999</v>
+        <v>52.2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>9.4</v>
-      </c>
+        <v>298.5</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>41.1</v>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>0.4</v>
+        <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>18.3</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>184</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1070,72 +1062,72 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7.2</v>
+        <v>377.9</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="F8" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
+        <v>441.2</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="J8" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="K8" s="3" t="n"/>
+      <c r="K8" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L8" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>5.1</v>
+      <c r="M8" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>2721.9</v>
+        <v>4971.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>1.2</v>
+        <v>99.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R8" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V8" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X8" s="8" t="n">
-        <v>92.8</v>
+      <c r="W8" s="8" t="n">
+        <v>917.8</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>83</v>
+        <v>185</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1150,71 +1142,69 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n"/>
+      <c r="C9" s="3" t="n">
+        <v>182528.1</v>
+      </c>
       <c r="D9" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>7.4</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>19.6</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>134.2</v>
+        <v>161.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>21.7</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>284.4</v>
+        <v>28.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>24.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="P9" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="n">
         <v>103.3</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>892.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>195.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>393.1</v>
-      </c>
-      <c r="U9" s="3" t="n"/>
+        <v>998.8</v>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" s="3" t="n">
-        <v>95.5</v>
+        <v>295.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>87.2</v>
+        <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>34.8</v>
+        <v>194.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>429</v>
+        <v>19429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>6.6</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1229,73 +1219,63 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="n">
+        <v>365</v>
+      </c>
       <c r="D10" s="3" t="n">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.6</v>
+        <v>14.3</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>61.5</v>
-      </c>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>11.9</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>637.9</v>
+      <c r="M10" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1.1</v>
+        <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="X10" s="8" t="n">
-        <v>90.09999999999999</v>
+        <v>19.1</v>
+      </c>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>3.2</v>
+        <v>38.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1311,75 +1291,69 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>7787.1</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2531
-228548177
-</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n">
-        <v>13.3</v>
+        <v>329.6</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>10.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" s="3" t="n"/>
+        <v>10.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="K11" s="3" t="n">
-        <v>7.7</v>
+        <v>17.9</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>221.3</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>19.5</v>
+        <v>92.8</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>811.4</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>289.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1.3</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>484.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>18.4</v>
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>20.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>98.8</v>
+      </c>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1394,72 +1368,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E12" s="3" t="n"/>
+        <v>521.2</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>13.9</v>
+      </c>
       <c r="F12" s="3" t="n">
         <v>4.1</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.8</v>
+        <v>41.3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="L12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277275
-163
-</t>
-        </is>
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99</v>
+        <v>299.9</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R12" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>1.9</v>
+      <c r="R12" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>18.1</v>
+        <v>188.6</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1.3</v>
+        <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>885</v>
+        <v>284</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>23.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1475,74 +1453,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
+        <v>9455.6</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>25.7</v>
-      </c>
       <c r="E13" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>23.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>113.8</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.9</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>44.7</v>
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>717.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P13" s="3" t="n"/>
+        <v>199</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>29.2</v>
+        <v>49.3</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>166.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>39.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26.8</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1557,45 +1537,47 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="3" t="n">
+        <v>20319.9</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>23.2</v>
+        <v>2.1</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>444.5</v>
+        <v>441.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="I14" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J14" s="8" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>9.9</v>
-      </c>
       <c r="L14" s="3" t="n">
-        <v>12.5</v>
+        <v>43.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>90.8</v>
+        <v>820.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>997.9</v>
+        <v>929</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1606,26 +1588,22 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="8" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>84.5</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>4.9</v>
+        <v>94</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1640,44 +1618,44 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
+      <c r="C15" s="3" t="n">
+        <v>484.5</v>
+      </c>
       <c r="D15" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="K15" s="3" t="n"/>
+        <v>20.9</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="n">
-        <v>4.4</v>
+        <v>44.1</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>8488.299999999999</v>
-      </c>
+        <v>14.1</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>922.6</v>
-      </c>
-      <c r="P15" s="3" t="n"/>
+        <v>97</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q15" s="3" t="n">
-        <v>25.7</v>
+        <v>2.1</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1686,25 +1664,21 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>13.2</v>
-      </c>
+        <v>948</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="n">
         <v>41.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>18.6</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.6</v>
+        <v>31.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1720,72 +1694,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>2326.9</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>127.2</v>
       </c>
-      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
-        <v>14.2</v>
+        <v>5.4</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>95.7</v>
+        <v>295.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>423.6</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>195481.9</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>3.4</v>
+        <v>113.9</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="M16" s="3" t="n"/>
+        <v>166.9</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>66.2</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>18.9</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>92.8</v>
+        <v>19491</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>6.2</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>18.7</v>
+        <v>115.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>12.1</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>941.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>42</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.3</v>
+        <v>5.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>100.4</v>
+        <v>10</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>22.3</v>
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>93.5</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>410.1</v>
+        <v>929</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1800,71 +1776,73 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="n">
+        <v>414.5</v>
+      </c>
       <c r="D17" s="8" t="n">
-        <v>57.9</v>
+        <v>59.2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>89.09999999999999</v>
+        <v>43</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>824.1</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>22.2</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>438.1</v>
-      </c>
-      <c r="P17" s="3" t="n"/>
+        <v>28.6</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="S17" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="S17" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>313</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>444.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>20.2</v>
+        <v>562.6</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>19.9</v>
+      <c r="X17" s="8" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>84.8</v>
+        <v>898</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.7</v>
+        <v>297.4</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1879,71 +1857,67 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="n">
+        <v>335.7</v>
+      </c>
       <c r="D18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="E18" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>39.7</v>
+        <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="H18" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>28.6</v>
-      </c>
+        <v>18.3</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>19</v>
+        <v>98</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>719</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>10.1</v>
+        <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>62.6</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n">
-        <v>76.7</v>
+        <v>11</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>22.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>634088</v>
+        <v>6.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1958,45 +1932,44 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 85 2
-</t>
-        </is>
+      <c r="C19" s="3" t="n">
+        <v>435.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>13.2</v>
+        <v>22.4</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1162.6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>92.09999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4</v>
+        <v>12.7</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>23.1</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>27.2</v>
+        <v>1.7</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
+        <v>4.3</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q19" s="3" t="n">
-        <v>1.4</v>
+        <v>14.3</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
@@ -2005,22 +1978,20 @@
         <v>13.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="W19" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>24.9</v>
+        <v>894.8</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2038,71 +2009,67 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="C20" s="3" t="n">
+        <v>494.9</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="8" t="n">
+        <v>1249.4</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H20" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>18.1</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.2</v>
+        <v>12.6</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>15.5</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
-        <v>96.8</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>221.4</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>5.1</v>
-      </c>
+        <v>17.5</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V20" s="3" t="n"/>
+        <v>92</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="W20" s="3" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>22.9</v>
-      </c>
+        <v>19.4</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
       <c r="Z20" s="3" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2117,74 +2084,70 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>379.3</v>
+      </c>
       <c r="D21" s="3" t="n">
-        <v>2.2</v>
+        <v>25.2</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="H21" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n">
-        <v>0.3</v>
+      <c r="I21" s="8" t="n">
+        <v>88.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.2</v>
+        <v>12.9</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.2</v>
+        <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="n">
-        <v>28.8</v>
+        <v>180</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>29.4</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="T21" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>4.2</v>
+        <v>94.7</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>169.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>18.6</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2198,74 +2161,70 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="n">
+        <v>508.9</v>
+      </c>
       <c r="D22" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n">
-        <v>0.6</v>
+        <v>45.8</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>10.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>12.1</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>51.7</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="R22" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>20.9</v>
+        <v>9.4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>12.2</v>
+        <v>16.1</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>89.2</v>
+        <v>18.9</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>18.6</v>
+        <v>36.1</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="Z22" s="3" t="inlineStr"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2280,74 +2239,74 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>128.2</v>
+        <v>2089.4</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>25.8</v>
+        <v>1128.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.8</v>
+        <v>162.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.2</v>
+        <v>4.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>6.9</v>
+        <v>1161.4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>16.6</v>
+        <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.5</v>
+        <v>110.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3.5</v>
+        <v>115.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.2</v>
+        <v>20.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>14.4</v>
-      </c>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>4.8</v>
+        <v>29489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.5</v>
+        <v>1113.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="S23" s="3" t="n"/>
+        <v>14.5</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>191.8</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>2328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>49.2</v>
+        <v>1219.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>94.3</v>
+        <v>194.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>86.3</v>
+        <v>186.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>26.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>9429</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>76.3</v>
+        <v>116.9</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2363,69 +2322,63 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
+        <v>43791.8</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n">
-        <v>53.1</v>
-      </c>
+        <v>13.4</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="8" t="n">
+        <v>21565.9</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="n">
-        <v>10.9</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>21.2</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n">
-        <v>23.1</v>
+        <v>97.8</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>39.9</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="n">
-        <v>328.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="W24" s="8" t="n">
-        <v>73.09999999999999</v>
-      </c>
+        <v>189.4</v>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
       <c r="X24" s="8" t="n">
-        <v>30040.7</v>
+        <v>8881.200000000001</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>85.8</v>
+      </c>
+      <c r="Z24" s="3" t="inlineStr"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2439,63 +2392,72 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="C25" s="3" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="E25" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>872.6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O25" s="3" t="n"/>
+      <c r="K25" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="n">
+        <v>198</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
+        <v>18.9</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
-      </c>
+        <v>111.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
+      <c r="V25" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W25" s="3" t="inlineStr"/>
       <c r="X25" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
+        <v>19.8</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2509,75 +2471,73 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>258.3</v>
+      </c>
       <c r="D26" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.2</v>
+        <v>22.4</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>118.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115178685
-1149791
-</t>
-        </is>
+        <v>2.1</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="I26" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>931.8</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>1.6</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2592,73 +2552,69 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n">
-        <v>22.4</v>
+      <c r="C27" s="3" t="n">
+        <v>535.8</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>224.5</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>118.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>91.2</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="8" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K27" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="n">
+        <v>199</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>18</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>12.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>19.1</v>
+        <v>28.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>3.9</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>15.6</v>
+        <v>3</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>12.6</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
       <c r="Y27" s="3" t="n">
-        <v>1</v>
+        <v>88.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>9.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2674,70 +2630,70 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2.4</v>
+        <v>331.3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>24.5</v>
+        <v>23.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I28" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
       <c r="J28" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K28" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>32.8</v>
+      </c>
       <c r="L28" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>161</v>
-      </c>
+        <v>44.5</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
       <c r="O28" s="3" t="n">
-        <v>936</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>19.8</v>
+        <v>98</v>
+      </c>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S28" s="8" t="n">
-        <v>41.1</v>
+        <v>42.2</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>17.6</v>
+        <v>41.2</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2752,75 +2708,71 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>309.1</v>
+      </c>
       <c r="D29" s="3" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>28.7</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="8" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
       <c r="J29" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>991</v>
+      </c>
+      <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0.4</v>
-      </c>
       <c r="Q29" s="3" t="n">
-        <v>424.1</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>12.1</v>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="n">
-        <v>8</v>
+        <v>856.1</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="W29" s="8" t="n">
+        <v>1991</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>19.2</v>
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>88</v>
+        <v>0.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2836,76 +2788,70 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
+        <v>1569.9</v>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>116.8</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>23.7</v>
-      </c>
       <c r="E30" s="3" t="n">
-        <v>14.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>18.5</v>
+        <v>194.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.9</v>
+        <v>1544.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>24.2</v>
+        <v>1629.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.6</v>
+        <v>176.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="M30" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>92</v>
+        <v>444924.4</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>61.2</v>
+        <v>212.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>23.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>19</v>
+        <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>14.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>66.7</v>
+        <v>9413.799999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>2.8</v>
+        <v>244.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>15.8</v>
+        <v>185.9</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>12.4</v>
-      </c>
+        <v>182.9</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>22.1</v>
+        <v>922</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2921,82 +2867,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-89191911
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>94.3</v>
+        <v>314</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.9</v>
+        <v>90.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="L31" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>9992.1</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>27.2</v>
+        <v>2.4</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>89.2</v>
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>413.2</v>
+        <v>8115.4</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>41.5</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>82.2</v>
+        <v>17</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>6.3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>4222.1</v>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81911955
-111
-</t>
-        </is>
+        <v>95</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3012,84 +2946,61 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.6</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.7</v>
+        <v>364.2</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>57.9</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="F32" s="3" t="n">
+        <v>411.1</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>2821.3</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K32" s="3" t="n">
-        <v>0.7</v>
+        <v>39.1</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>14.9</v>
+        <v>0.9</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>200.7</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>99</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
+        <v>14.8</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>19.4</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr"/>
+      <c r="W32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="n">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18 1
-</t>
-        </is>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3104,74 +3015,70 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>440.2</v>
+        <v>411.2</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>181.3</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>14.9</v>
+      <c r="M33" s="8" t="n">
+        <v>1097.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>29</v>
+        <v>99.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="U33" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="8" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W33" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="V33" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>12.1</v>
+      <c r="X33" s="8" t="n">
+        <v>980</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>96</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.2</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3187,74 +3094,68 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>22.2</v>
+        <v>1144.4</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>19.7</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13.7</v>
+        <v>15.1</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>18.2</v>
+        <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J34" s="3" t="n"/>
+        <v>94.59999999999999</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="K34" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>29.2</v>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>6.6</v>
+        <v>18.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>21.2</v>
+        <v>16.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>77.8</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>17.8</v>
+        <v>21</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>16.5</v>
+        <v>43.2</v>
+      </c>
+      <c r="X34" s="8" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3270,74 +3171,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>22.7</v>
+        <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H35" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>3.5</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>45.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>21281.8</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>19.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>292</v>
+        <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R35" s="3" t="n"/>
+        <v>23.9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>23.3</v>
+      </c>
       <c r="S35" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>986.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="3" t="n">
-        <v>2.9</v>
+        <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>26.4</v>
+        <v>48.4</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>522.2</v>
+        <v>6.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>12.2</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>38.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3352,75 +3253,73 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>613.2</v>
+      </c>
       <c r="D36" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="G36" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.9</v>
+        <v>14.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>115</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>16.9</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>1.8</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>23.9</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>66.5</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>12.1</v>
+        <v>41.2</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>32.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.8</v>
+        <v>10.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3435,85 +3334,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>19782.4</v>
+      </c>
       <c r="D37" s="3" t="n">
-        <v>4.5</v>
+        <v>1118.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422112
-214101
-</t>
-        </is>
+        <v>0.6</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1092.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">455266
-72
-45
-61194929
-</t>
-        </is>
+        <v>32.8</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>56.9</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>4.8</v>
+        <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>4.8</v>
+        <v>150.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>52.5</v>
+        <v>1681.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>14.6</v>
+        <v>167.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>6</v>
+        <v>18.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>97.8</v>
+        <v>9492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>24.9</v>
+        <v>401.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.6</v>
+        <v>189.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>219.1</v>
+        <v>382191.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>2.4</v>
+        <v>233.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>99</v>
+        <v>20.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>181.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7.4</v>
+        <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>422.5</v>
+        <v>42.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>12.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3529,72 +3420,68 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>484.1</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>32.2</v>
+        <v>495.6</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="8" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="M38" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr"/>
+      <c r="M38" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="N38" s="3" t="n">
-        <v>15.4</v>
+        <v>12.9</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>496</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>72.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>401.2</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>2.6</v>
+        <v>30.2</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>172</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>380.9</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>16.3</v>
-      </c>
+        <v>76.2</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>8101.4</v>
+      </c>
+      <c r="W38" s="3" t="inlineStr"/>
       <c r="X38" s="3" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>15.9</v>
+        <v>184.6</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3610,74 +3497,66 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>14.3</v>
+        <v>624.3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>23.7</v>
+        <v>25.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.4</v>
+        <v>11.9</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>181.5</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I39" s="3" t="n"/>
+        <v>17.6</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
       <c r="J39" s="3" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-141
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>15.4</v>
+        <v>8</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="8" t="n">
+        <v>2120.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>26.2</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>12.5</v>
+        <v>18.9</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>50.5</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>7.4</v>
+        <v>126</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y39" s="3" t="n"/>
+        <v>12.8</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="3" t="inlineStr"/>
+      <c r="X39" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>162.8</v>
+      </c>
       <c r="Z39" s="3" t="n">
         <v>3.2</v>
       </c>
@@ -3694,79 +3573,75 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-6443
-</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.9</v>
+      <c r="C40" s="3" t="n">
+        <v>637.7</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>21.7</v>
+        <v>12.7</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>1.3</v>
+        <v>10</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>12</v>
+        <v>19.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>99.8</v>
+        <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>29.5</v>
+        <v>19.4</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>6</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="V40" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="V40" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>16.1</v>
+        <v>3.1</v>
+      </c>
+      <c r="X40" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>62.8</v>
+        <v>59</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1.8</v>
+        <v>26.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3781,73 +3656,67 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="F41" s="3" t="n">
+      <c r="C41" s="3" t="n">
+        <v>794.3</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
+      <c r="P41" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="3" t="inlineStr"/>
+      <c r="S41" s="3" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="V41" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>16.2</v>
-      </c>
       <c r="X41" s="8" t="n">
-        <v>85.3</v>
+        <v>22.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1.8</v>
+        <v>26.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3866,65 +3735,69 @@
         <v>608.8</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>470.9</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="I42" s="3" t="n">
-        <v>47.2</v>
+        <v>19</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.6</v>
+        <v>35.9</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="M42" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="M42" s="3" t="inlineStr"/>
       <c r="N42" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>98</v>
-      </c>
+        <v>93.2</v>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
+        <v>26.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="T42" s="3" t="n">
-        <v>48</v>
+        <v>949</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="W42" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="W42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>4.4</v>
+        <v>15.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>162.8</v>
+        <v>18.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3940,70 +3813,68 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>6094.4</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>18.7</v>
-      </c>
+        <v>604.4</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H43" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K43" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="L43" s="3" t="n">
+        <v>434</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
+        <v>192</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>18.2</v>
+        <v>39.9</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>18.1</v>
+        <v>15.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>53.2</v>
+        <v>729.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>6.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4018,72 +3889,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4101,71 +3930,73 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>67272.7</v>
+        <v>431.1</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-24222
-</t>
-        </is>
+        <v>3.6</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="J45" s="3" t="n"/>
+        <v>1181.9</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>27.2</v>
+      </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>602.2</v>
-      </c>
-      <c r="M45" s="3" t="n"/>
+        <v>356.4</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>55.9</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>6197.2</v>
+        <v>168.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>624.2</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>496</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>124.8</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>126.3</v>
+        <v>1126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>827.2</v>
+        <v>18</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>218.1</v>
+        <v>1282.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>29.8</v>
+        <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1208.9</v>
+        <v>1108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>1060.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>37.8</v>
+        <v>23028.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4181,69 +4012,65 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>32.1</v>
+        <v>223.9</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>26.2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>15.5</v>
+        <v>40.5</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>503.4</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="I46" s="8" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>55.9</v>
+      <c r="I46" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>49</v>
-      </c>
+        <v>13.9</v>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="U46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="8" t="n">
+        <v>865.4</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V46" s="8" t="n">
-        <v>2918</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -738,48 +738,50 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
+      <c r="G4" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="8" t="n">
-        <v>10.8</v>
+      <c r="I4" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>27.8</v>
+        <v>27</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99.8</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="P4" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>21.1</v>
+        <v>19.7</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>89.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
@@ -787,21 +789,23 @@
       <c r="T4" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="V4" s="3" t="n">
-        <v>43.2</v>
+        <v>17.8</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>4.6</v>
+        <v>10.9</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -817,33 +821,33 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1564.3</v>
-      </c>
-      <c r="D5" s="8" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0.1</v>
+      <c r="E5" s="8" t="n">
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>42.5</v>
+        <v>12.5</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" s="8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -853,13 +857,15 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+        <v>95.8</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -872,19 +878,19 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>293</v>
+        <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -903,71 +909,73 @@
         <v>338</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>19.3</v>
+        <v>1.9</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1</v>
+        <v>10.1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1141.6</v>
+        <v>110.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>994.2</v>
+        <v>14.5</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>16.1</v>
+        <v>21562.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>1.9</v>
+        <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>44.4</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>671.8</v>
+        <v>62.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.2</v>
+        <v>18.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1103.9</v>
+        <v>1.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -983,52 +991,56 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>355.7</v>
+        <v>255.2</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>80.09999999999999</v>
+      <c r="G7" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.3</v>
+        <v>11.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>41.4</v>
+        <v>19.4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>52.2</v>
+        <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>298.5</v>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="S7" s="3" t="inlineStr"/>
+        <v>17.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T7" s="3" t="n">
         <v>77</v>
       </c>
@@ -1036,14 +1048,16 @@
         <v>9.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>184</v>
+        <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.5</v>
@@ -1062,7 +1076,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
+        <v>377.8</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
@@ -1070,64 +1084,68 @@
       <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="H8" s="3" t="n">
-        <v>441.2</v>
+        <v>14.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="3" t="n">
-        <v>5.2</v>
+      <c r="L8" s="8" t="n">
+        <v>15.2</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>4971.2</v>
+        <v>31.4</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>99.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R8" s="8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>917.8</v>
+        <v>29.8</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>97.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1143,68 +1161,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182528.1</v>
+        <v>1825.2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+        <v>126.5</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>71.5</v>
+      </c>
       <c r="F9" s="3" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>161.5</v>
+        <v>61.5</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.7</v>
+        <v>19.7</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>28.9</v>
+        <v>1281.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
+        <v>423.8</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>103.3</v>
+        <v>10.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>195.6</v>
+        <v>985.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>998.8</v>
-      </c>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>910.1</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>295.3</v>
+        <v>95.5</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>194.8</v>
+        <v>949.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>19429</v>
+        <v>94290.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1220,41 +1246,49 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>365</v>
+        <v>3650.1</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>14.3</v>
+        <v>1.4</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>41.2</v>
+      </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16.8</v>
+        <v>11.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="n">
+        <v>83.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>18</v>
@@ -1265,17 +1299,23 @@
       <c r="T10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>17.4</v>
+      </c>
       <c r="X10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>85.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>38.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1296,64 +1336,72 @@
       <c r="D11" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="E11" s="8" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>13.9</v>
+      </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="8" t="n">
-        <v>1.6</v>
+        <v>12.8</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>23.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>42.6</v>
+        <v>91.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>80.2</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>811.4</v>
-      </c>
-      <c r="S11" s="8" t="n">
-        <v>289.5</v>
+        <v>62.3</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>18.6</v>
+        <v>15</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>20.4</v>
+      <c r="X11" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1368,76 +1416,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>521.2</v>
+        <v>581.1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>31.7</v>
+        <v>51.7</v>
       </c>
       <c r="E12" s="8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>17.2</v>
-      </c>
       <c r="S12" s="8" t="n">
-        <v>46.9</v>
+        <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.6</v>
+        <v>14104.6</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>284</v>
+        <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>23.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1453,25 +1501,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>9455.6</v>
+        <v>555.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>11.6</v>
+      <c r="E13" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>113.8</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.6</v>
+        <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1480,49 +1528,47 @@
         <v>8</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>41.1</v>
+        <v>11.1</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>717.6</v>
+        <v>19.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>49.3</v>
+        <v>19.2</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>66.8</v>
+      </c>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>7.8</v>
+      <c r="W13" s="8" t="n">
+        <v>97.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1538,46 +1584,46 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>20319.9</v>
+        <v>31.8</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.1</v>
+        <v>12.3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>441.5</v>
+        <v>19.7</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>4.5</v>
       </c>
       <c r="H14" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>12.9</v>
-      </c>
       <c r="J14" s="3" t="n">
-        <v>31.6</v>
+        <v>9.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>43.5</v>
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>820.2</v>
+        <v>12.5</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>84.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>929</v>
+        <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1588,22 +1634,26 @@
       <c r="S14" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="8" t="n">
-        <v>71.8</v>
+      <c r="T14" s="3" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>104.6</v>
+        <v>20.6</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>18.4</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>25.2</v>
+      </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1624,38 +1674,44 @@
       <c r="D15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>19.1</v>
+      <c r="E15" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>29.6</v>
+        <v>20.4</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>12082.1</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="L15" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>2.1</v>
+      <c r="P15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>17.8</v>
@@ -1664,18 +1720,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>948</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
+        <v>9648</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17.2</v>
+      </c>
       <c r="V15" s="3" t="n">
-        <v>41.2</v>
+        <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
+        <v>17.5</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>824.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1694,47 +1754,49 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2326.9</v>
+        <v>23069.1</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>127.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.4</v>
+        <v>64.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>295.7</v>
+        <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>195481.9</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>139.7</v>
+      </c>
       <c r="J16" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>166.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>66.2</v>
+        <v>6.6</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>19491</v>
+        <v>481.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>1115.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1746,22 +1808,22 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>5.3</v>
+        <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>10</v>
+        <v>1100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>190.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>9.9</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1777,72 +1839,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>414.5</v>
+        <v>4814.1</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>43</v>
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>119.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>824.1</v>
+        <v>12.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>19.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="J17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L17" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.1</v>
+        <v>11.8</v>
       </c>
       <c r="S17" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>562.6</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>1.4</v>
+      <c r="V17" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X17" s="8" t="n">
-        <v>99.59999999999999</v>
+      <c r="X17" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>898</v>
+        <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>297.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1858,10 +1924,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>335.7</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>23.9</v>
+        <v>955.7</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>14.3</v>
@@ -1870,54 +1936,64 @@
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H18" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K18" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+        <v>22.6</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="M18" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>182.2</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
+        <v>980.9</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10.4</v>
+      </c>
       <c r="Q18" s="8" t="n">
-        <v>22.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>719</v>
+        <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W18" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>6.2</v>
+        <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.6</v>
+        <v>17.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1933,65 +2009,71 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
+        <v>455.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>22.4</v>
+        <v>25.7</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1162.6</v>
+        <v>69</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>19.3</v>
+        <v>199.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>64.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>13.8</v>
+        <v>10.8</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>196.8</v>
+        <v>41.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>14.3</v>
+        <v>24.3</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>13.4</v>
+      <c r="S19" s="8" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U19" s="3" t="inlineStr"/>
+        <v>36.1</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>29.4</v>
+      </c>
       <c r="V19" s="8" t="n">
-        <v>19.9</v>
+        <v>199.5</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>17.5</v>
+        <v>98.5</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>894.8</v>
+        <v>84</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.6</v>
@@ -2010,43 +2092,47 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>494.9</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
+        <v>1494.9</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="E20" s="8" t="n">
-        <v>1249.4</v>
+        <v>12.1</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G20" s="8" t="n">
+        <v>195.8</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>14.3</v>
+      </c>
       <c r="J20" s="3" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>221.4</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>3.5</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
@@ -2054,22 +2140,26 @@
       <c r="S20" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>188</v>
+      </c>
       <c r="U20" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V20" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>43.4</v>
+      <c r="W20" s="8" t="n">
+        <v>58.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr"/>
+        <v>19.1</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="Z20" s="3" t="n">
-        <v>21.9</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2085,28 +2175,28 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>13.8</v>
+        <v>371.3</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>91608</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>179.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>88.8</v>
+        <v>89.5</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.9</v>
+        <v>2.7</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>21.1</v>
@@ -2114,15 +2204,17 @@
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="M21" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>88.7</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>180</v>
+        <v>1808</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
@@ -2131,22 +2223,26 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>80.90000000000001</v>
+      </c>
       <c r="U21" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="V21" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>169.4</v>
+        <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2164,19 +2260,19 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>45.8</v>
+      <c r="D22" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>29.5</v>
+        <v>13.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H22" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2186,45 +2282,51 @@
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
-      <c r="L22" s="8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P22" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="8" t="n">
+      <c r="Q22" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.3</v>
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V22" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>36.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2245,68 +2347,70 @@
         <v>1128.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>162.8</v>
+        <v>66.8</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.5</v>
+        <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1161.4</v>
+        <v>18.5</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>110.9</v>
+        <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>115.9</v>
+        <v>15.9</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>20.5</v>
+        <v>207.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>29489</v>
+        <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1113.6</v>
+        <v>11513.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>14.5</v>
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2328</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>1219.8</v>
+        <v>149.8</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>186.3</v>
+        <v>8.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>938.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>9429</v>
+        <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.9</v>
+        <v>1196.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2322,63 +2426,77 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>43791.8</v>
+        <v>4972.9</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
+      <c r="F24" s="8" t="n">
+        <v>19.5</v>
+      </c>
       <c r="G24" s="8" t="n">
-        <v>21565.9</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>59.7</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>5.4</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>4.4</v>
+        <v>14.7</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="8" t="n">
+        <v>18</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="S24" s="3" t="inlineStr"/>
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R24" s="8" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="T24" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>189.4</v>
-      </c>
-      <c r="W24" s="3" t="inlineStr"/>
-      <c r="X24" s="8" t="n">
-        <v>8881.200000000001</v>
+        <v>89.40000000000001</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
-      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2393,70 +2511,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>253.6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>872.6</v>
+        <v>2.3</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>13.6</v>
+        <v>2135.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8</v>
+        <v>81.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>16.6</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+        <v>96.2</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>22</v>
+      </c>
       <c r="X25" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>98</v>
+        <v>93.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2472,19 +2596,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>258.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>118.9</v>
+        <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.1</v>
+        <v>17.7</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.5</v>
@@ -2493,51 +2617,55 @@
         <v>0.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>115.8</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>88808</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>931.8</v>
+        <v>98</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>17.2</v>
+        <v>11.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2553,46 +2681,52 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>535.8</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>224.5</v>
-      </c>
-      <c r="E27" s="8" t="n">
+        <v>9351.700000000001</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>118.9</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>91.2</v>
+      <c r="F27" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>1312.5</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr"/>
+        <v>11.6</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>11.7</v>
+      </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>13.2</v>
+      </c>
       <c r="L27" s="8" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
+        <v>73.5</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>28.1</v>
@@ -2603,15 +2737,17 @@
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>19</v>
+      <c r="V27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>88.8</v>
+        <v>28</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2630,7 +2766,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.3</v>
+        <v>331.8</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>23.7</v>
@@ -2638,53 +2774,59 @@
       <c r="E28" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <v>181.7</v>
+      <c r="F28" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
+      <c r="I28" s="8" t="n">
+        <v>7.5</v>
+      </c>
       <c r="J28" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K28" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K28" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O28" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="8" t="n">
+      <c r="P28" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>42.2</v>
+      <c r="R28" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>4.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>41.2</v>
+      <c r="W28" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>19.2</v>
@@ -2715,64 +2857,70 @@
         <v>23.1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="8" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>16.6</v>
+        <v>0.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>82.8</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>991</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="S29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>856.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="W29" s="8" t="n">
-        <v>1991</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+      <c r="V29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2797,61 +2945,67 @@
         <v>71.90000000000001</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>194.3</v>
+        <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1544.9</v>
+        <v>649.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1629.4</v>
+        <v>62.9</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>176.9</v>
+        <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+        <v>74.90000000000001</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>8.9</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>444924.4</v>
+        <v>491</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>212.1</v>
+        <v>412.1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>998.9</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>9413.799999999999</v>
+        <v>4135.1</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>244.4</v>
+        <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>185.9</v>
+        <v>85.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>829.4</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>92.09999999999999</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>922</v>
+        <v>6548</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2869,8 +3023,8 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>23.4</v>
+      <c r="D31" s="8" t="n">
+        <v>23.9</v>
       </c>
       <c r="E31" s="8" t="n">
         <v>14.9</v>
@@ -2879,58 +3033,60 @@
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="H31" s="3" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H31" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="L31" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="M31" s="8" t="n">
+        <v>19.9</v>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>1454.4</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
+      <c r="R31" s="8" t="n">
+        <v>7.8</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>8115.4</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>18.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>8010.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2948,40 +3104,42 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>411.1</v>
+      <c r="D32" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>31.9</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>2821.3</v>
+        <v>81</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
+        <v>82.90000000000001</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>11.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
+        <v>79.3</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>19.6</v>
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.9</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n">
-        <v>10.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>13</v>
@@ -2989,18 +3147,30 @@
       <c r="R32" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V32" s="3" t="inlineStr"/>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
+        <v>8.4</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>181.7</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3021,64 +3191,70 @@
         <v>23.7</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>181.7</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="3" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>1097.2</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>62.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr"/>
-      <c r="U33" s="8" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="V33" s="3" t="n">
+      <c r="Q33" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>1.4</v>
+      <c r="W33" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>980</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3094,68 +3270,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1144.4</v>
+        <v>211.4</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>15.1</v>
+        <v>197.2</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>159.7</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>14.2</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2.5</v>
+        <v>98.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>5.2</v>
+      </c>
       <c r="N34" s="3" t="n">
-        <v>18.8</v>
+        <v>91.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr"/>
-      <c r="U34" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>16.9</v>
-      </c>
       <c r="W34" s="3" t="n">
-        <v>43.2</v>
+        <v>15.2</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>16.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>90.8</v>
+        <v>20</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3174,13 +3358,13 @@
         <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>142.1</v>
+        <v>22.2</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>18.1</v>
+        <v>181.8</v>
       </c>
       <c r="G35" s="8" t="n">
         <v>12.1</v>
@@ -3192,7 +3376,7 @@
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.9</v>
+        <v>9.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3200,11 +3384,11 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>21281.8</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>19.9</v>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
@@ -3213,32 +3397,34 @@
         <v>0.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>23.9</v>
+        <v>29.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="T35" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>68.8</v>
+      </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>48.4</v>
+        <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>17.7</v>
+        <v>18.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3257,69 +3443,73 @@
         <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>23.1</v>
+        <v>25.7</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>449.5</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>11.3</v>
+        <v>713.8</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>10.9</v>
+        <v>105.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.3</v>
+        <v>93.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>16.4</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>27</v>
+        <v>18.8</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="T36" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="U36" s="3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>32.6</v>
+        <v>17.2</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>10.8</v>
+        <v>28.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3335,76 +3525,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>19782.4</v>
+        <v>2078.2</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>1118.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1092.2</v>
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.8</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.9</v>
+        <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>819.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>150.1</v>
+        <v>5071.7</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1681.5</v>
+        <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>167.6</v>
+        <v>62.6</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>9492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>401.2</v>
+        <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>189.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>382191.4</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>233.2</v>
+        <v>93.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.9</v>
+        <v>90</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>181.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>42.9</v>
+        <v>429.9</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>6.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3422,66 +3612,74 @@
       <c r="C38" s="3" t="n">
         <v>495.6</v>
       </c>
-      <c r="D38" s="3" t="inlineStr"/>
+      <c r="D38" s="8" t="n">
+        <v>23.7</v>
+      </c>
       <c r="E38" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>12.4</v>
+        <v>84.90000000000001</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>25.1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>91.3</v>
+        <v>61.5</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.9</v>
+        <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>18.2</v>
+        <v>20.2</v>
+      </c>
+      <c r="R38" s="8" t="n">
+        <v>117</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
-      <c r="U38" s="8" t="n">
-        <v>66.40000000000001</v>
+      <c r="U38" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>8101.4</v>
-      </c>
-      <c r="W38" s="3" t="inlineStr"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>16.3</v>
+      </c>
       <c r="X38" s="3" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>184.6</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>81.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3497,68 +3695,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
+        <v>664.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>181.5</v>
+      <c r="F39" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I39" s="3" t="inlineStr"/>
+        <v>7.6</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J39" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="8" t="n">
-        <v>2120.2</v>
+        <v>8.1</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P39" s="8" t="n">
+      <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>24.8</v>
+        <v>69.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>50.5</v>
+        <v>521</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="8" t="n">
-        <v>98.8</v>
+      <c r="V39" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>162.8</v>
+        <v>64</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>3.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3576,17 +3782,17 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>16.3</v>
+        <v>11.6</v>
       </c>
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="3" t="n">
@@ -3596,52 +3802,52 @@
         <v>5.7</v>
       </c>
       <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>110</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>21.9</v>
+      <c r="N40" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>35.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>25.9</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0.2</v>
+        <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="8" t="n">
-        <v>22.3</v>
+      <c r="V40" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X40" s="8" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>59</v>
+        <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3657,66 +3863,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>794.3</v>
+        <v>694.3</v>
       </c>
       <c r="D41" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
+      <c r="E41" s="8" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="J41" s="3" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>110.7</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R41" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>293.5</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>58.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>17.9</v>
+        <v>12</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="W41" s="8" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="8" t="n">
-        <v>22.8</v>
+      <c r="X41" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>26.8</v>
+        <v>28.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3732,72 +3948,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>608.8</v>
+        <v>208.8</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>470.9</v>
+        <v>10.4</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>160.5</v>
+        <v>181.7</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>15.8</v>
+        <v>53.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>35.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M42" s="3" t="inlineStr"/>
+      <c r="L42" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N42" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="O42" s="3" t="inlineStr"/>
+        <v>18.1</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>949</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>49</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>47.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.2</v>
+        <v>28.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3813,39 +4033,45 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>604.4</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="D43" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="E43" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>81</v>
+        <v>1627.9</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K43" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="3" t="n">
-        <v>434</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
+      <c r="L43" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>1021.9</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
+        <v>97</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
       </c>
@@ -3856,25 +4082,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>92.8</v>
+        <v>2.8</v>
       </c>
       <c r="U43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Y43" s="3" t="n">
         <v>39.9</v>
       </c>
-      <c r="V43" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>729.8</v>
-      </c>
       <c r="Z43" s="3" t="n">
-        <v>20.3</v>
+        <v>211.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3889,7 +4115,9 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
@@ -3930,13 +4158,13 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>431.1</v>
+        <v>131.9</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>3.6</v>
+        <v>23.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -3945,58 +4173,58 @@
         <v>32.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1181.9</v>
+        <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>356.4</v>
+        <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>168.9</v>
+        <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>124.8</v>
+        <v>121</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1126.3</v>
+        <v>126.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>29.2</v>
+        <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1282.2</v>
+        <v>212.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>1108.9</v>
+        <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1060.9</v>
+        <v>658</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>23028.1</v>
+        <v>382.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.5</v>
+        <v>281.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4014,63 +4242,73 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>40.5</v>
+      <c r="E46" s="8" t="n">
+        <v>101.5</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>81.5</v>
+        <v>181.5</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>503.4</v>
+        <v>200.4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>3.8</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>1111</v>
+      </c>
       <c r="L46" s="8" t="n">
-        <v>111.3</v>
+        <v>1219.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>35.3</v>
+        <v>111.9</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>900.1</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>59.8</v>
+      </c>
       <c r="U46" s="8" t="n">
         <v>865.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>16.6</v>
-      </c>
+        <v>1541.6</v>
+      </c>
+      <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>181.4</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -766,28 +766,28 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>15.7</v>
+        <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>20.2</v>
+        <v>99</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="R4" s="8" t="n">
-        <v>89.3</v>
+      <c r="R4" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
@@ -795,8 +795,8 @@
       <c r="V4" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>12</v>
+      <c r="W4" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>18.9</v>
@@ -805,7 +805,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -821,16 +821,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>164.5</v>
+        <v>14649.5</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>12.5</v>
@@ -845,7 +845,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8.1</v>
+        <v>0.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>14</v>
@@ -857,7 +857,7 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>95.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.4</v>
@@ -878,9 +878,9 @@
         <v>4.8</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W5" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -890,7 +890,7 @@
         <v>93</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -908,20 +908,20 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>4.9</v>
+      <c r="D6" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F6" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>110.6</v>
+      <c r="H6" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>11.2</v>
@@ -930,23 +930,21 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.6</v>
+        <v>14.2</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>21562.1</v>
+        <v>256.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -969,13 +967,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>20</v>
+        <v>29.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -991,7 +989,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>255.2</v>
+        <v>353.7</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>25.3</v>
@@ -999,7 +997,7 @@
       <c r="E7" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" s="3" t="n">
@@ -1018,7 +1016,7 @@
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>15.2</v>
@@ -1027,7 +1025,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1039,13 +1037,13 @@
         <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>77</v>
+        <v>7.7</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
@@ -1076,16 +1074,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.8</v>
+        <v>377.9</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>19.2</v>
+      <c r="F8" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>9</v>
@@ -1096,26 +1094,26 @@
       <c r="I8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>14.1</v>
+      <c r="J8" s="3" t="n">
+        <v>11.7</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>31.4</v>
+        <v>13.1</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>99.8</v>
+        <v>4.1</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>22.7</v>
@@ -1132,11 +1130,11 @@
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>29.8</v>
+      <c r="V8" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>97.8</v>
+        <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>19.2</v>
@@ -1167,13 +1165,13 @@
         <v>126.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>99</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>61.5</v>
@@ -1181,38 +1179,36 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>19.7</v>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>1281.9</v>
+        <v>28.9</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>423.8</v>
+        <v>422</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>7.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.3</v>
+        <v>103.3</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>985.6</v>
+        <v>9285.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>910.1</v>
+        <v>891.1</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1224,13 +1220,13 @@
         <v>871.2</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>949.8</v>
+        <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>94290.8</v>
+        <v>9429.799999999999</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>16.7</v>
+        <v>116.9</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1252,40 +1248,40 @@
         <v>25.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.4</v>
+        <v>14.3</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>41.2</v>
+        <v>12.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>58</v>
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>83.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>2</v>
@@ -1297,15 +1293,15 @@
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1334,13 +1330,13 @@
         <v>329.6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>13.9</v>
+        <v>33.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1355,49 +1351,49 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>12.8</v>
+        <v>17.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>52.7</v>
+        <v>5.7</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.6</v>
+        <v>231.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>80.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>62.3</v>
+        <v>2.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>21.9</v>
+      <c r="S11" s="8" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>15</v>
+        <v>188.6</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>28.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>99.8</v>
+        <v>98.8</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>1</v>
@@ -1416,58 +1412,56 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>581.1</v>
+        <v>501.1</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>51.7</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>53.9</v>
+      <c r="E12" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="R12" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="S12" s="8" t="n">
+      <c r="R12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>14104.6</v>
+        <v>18.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1485,7 +1479,7 @@
         <v>89</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1501,19 +1495,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>555.6</v>
+        <v>155.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>87.09999999999999</v>
+      <c r="E13" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1527,20 +1521,20 @@
       <c r="K13" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="3" t="n">
-        <v>11.1</v>
+      <c r="L13" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>19.6</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>13.1</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1548,18 +1542,20 @@
       <c r="R13" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>19.7</v>
+      <c r="S13" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="U13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V13" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>97.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
@@ -1568,7 +1564,7 @@
         <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1584,9 +1580,9 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="D14" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -1596,7 +1592,7 @@
         <v>19.7</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>8.9</v>
@@ -1605,10 +1601,10 @@
         <v>2.9</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>12.5</v>
@@ -1616,8 +1612,8 @@
       <c r="M14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>84.3</v>
+      <c r="N14" s="8" t="n">
+        <v>94.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
@@ -1635,19 +1631,19 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>171.1</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>17.8</v>
+        <v>7.9</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="8" t="n">
-        <v>18.4</v>
+      <c r="W14" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>25.2</v>
+        <v>86.2</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
@@ -1669,12 +1665,12 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>484.5</v>
+        <v>454.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="F15" s="3" t="n">
@@ -1683,11 +1679,11 @@
       <c r="G15" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>12082.1</v>
+      <c r="H15" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>11.4</v>
+        <v>0.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1696,13 +1692,13 @@
         <v>11.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>19.9</v>
+        <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>12.7</v>
+        <v>18.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>97</v>
@@ -1710,7 +1706,7 @@
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1720,22 +1716,22 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>9648</v>
-      </c>
-      <c r="U15" s="8" t="n">
+        <v>248</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.6</v>
+        <v>1.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>824.8</v>
+        <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>31.6</v>
@@ -1754,13 +1750,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>23069.1</v>
+        <v>2306.9</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>127.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>64.3</v>
+        <v>655.3</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>95.7</v>
@@ -1769,34 +1765,34 @@
         <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>58.9</v>
+        <v>48.9</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>139.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
+        <v>134.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>70.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>481.8</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1115.7</v>
+        <v>118.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1811,16 +1807,16 @@
         <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1100.4</v>
+        <v>100.9</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>9421</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1839,19 +1835,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4814.1</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>25.9</v>
+        <v>814.1</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>97.09999999999999</v>
+      <c r="F17" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1859,23 +1855,23 @@
       <c r="I17" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>16.4</v>
+      <c r="J17" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.6</v>
+        <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98.8</v>
+        <v>28.6</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1886,7 +1882,7 @@
       <c r="R17" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="S17" s="8" t="n">
+      <c r="S17" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="T17" s="3" t="n">
@@ -1908,7 +1904,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1926,8 +1922,8 @@
       <c r="C18" s="3" t="n">
         <v>955.7</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>0.9</v>
+      <c r="D18" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>14.3</v>
@@ -1936,37 +1932,35 @@
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="H18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.5</v>
+        <v>25.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>22.6</v>
+        <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>182.2</v>
+        <v>18</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>980.9</v>
+        <v>982.8</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>66.40000000000001</v>
+        <v>216.8</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>19</v>
@@ -1975,25 +1969,25 @@
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>68</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2009,16 +2003,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>455.6</v>
+        <v>435.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>199.3</v>
+        <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>1.2</v>
@@ -2030,47 +2024,49 @@
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>14.3</v>
+        <v>1.3</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>15.5</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>41.8</v>
+        <v>92.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="8" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="W19" s="8" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>28.9</v>
+        <v>19.9</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>88.90000000000001</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2092,16 +2088,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1494.9</v>
+        <v>1497.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>12.1</v>
+        <v>22.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>195.8</v>
+        <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.8</v>
@@ -2110,18 +2106,18 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>14.3</v>
+        <v>2.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="M20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
@@ -2129,34 +2125,34 @@
         <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>3.5</v>
+        <v>23.9</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>188</v>
+        <v>2.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>12</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>19.2</v>
+        <v>91.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>58.8</v>
+        <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>8</v>
@@ -2177,23 +2173,23 @@
       <c r="C21" s="3" t="n">
         <v>371.3</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>3.6</v>
+      <c r="D21" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>91608</v>
+        <v>14.8</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>89.5</v>
+        <v>15.6</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
@@ -2211,7 +2207,7 @@
         <v>88.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1808</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>8</v>
@@ -2223,25 +2219,25 @@
         <v>18.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="Z21" s="3" t="inlineStr"/>
       <c r="AA21" s="3" t="inlineStr">
@@ -2260,17 +2256,17 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2278,39 +2274,41 @@
       <c r="I22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="K22" s="3" t="n">
         <v>51.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>21.4</v>
+        <v>1.3</v>
+      </c>
+      <c r="M22" s="8" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>4.6</v>
+        <v>224.6</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>18.7</v>
+        <v>185.4</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>1.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2319,7 +2317,7 @@
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>20.1</v>
+        <v>28.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2344,7 +2342,7 @@
         <v>2089.4</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1128.5</v>
+        <v>1128.4</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>66.8</v>
@@ -2353,7 +2351,7 @@
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
@@ -2368,49 +2366,45 @@
         <v>27.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>207.1</v>
+        <v>20.7</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6.9</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.8</v>
+        <v>71.8</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>11513.6</v>
+        <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>91.8</v>
-      </c>
+        <v>918.5</v>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>328</v>
+        <v>3260.6</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
+        <v>49.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>8.6</v>
+        <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>938.9</v>
+        <v>93.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1196.3</v>
+        <v>198.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2426,10 +2420,10 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4972.9</v>
+        <v>4912.9</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>25.6</v>
+        <v>35.6</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>13.4</v>
@@ -2440,44 +2434,42 @@
       <c r="G24" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>8.5</v>
+      <c r="H24" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>5.4</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>14.7</v>
+        <v>1.4</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>18</v>
+      <c r="N24" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>85.3</v>
+      <c r="P24" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>6.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
@@ -2485,8 +2477,8 @@
       <c r="V24" s="8" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="W24" s="8" t="n">
-        <v>73.09999999999999</v>
+      <c r="W24" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>18.7</v>
@@ -2495,7 +2487,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2511,49 +2503,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>253.6</v>
+        <v>223.6</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>153.9</v>
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>2135.6</v>
+        <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>81.7</v>
+        <v>8.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>96.2</v>
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>10.2</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>12.1</v>
+      <c r="N25" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2562,25 +2554,25 @@
         <v>18.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>22</v>
+      <c r="W25" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>93.8</v>
+        <v>920.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2604,21 +2596,19 @@
       <c r="E26" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
@@ -2626,18 +2616,18 @@
         <v>15.8</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>88808</v>
+        <v>908.8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q26" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
@@ -2647,7 +2637,7 @@
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2656,13 +2646,13 @@
         <v>15.6</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>11.2</v>
+        <v>15.3</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0.6</v>
@@ -2681,7 +2671,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9351.700000000001</v>
+        <v>435.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.5</v>
@@ -2693,13 +2683,13 @@
         <v>18.9</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>1312.5</v>
-      </c>
-      <c r="H27" s="8" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="I27" s="8" t="n">
-        <v>11.7</v>
+      <c r="I27" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2708,21 +2698,21 @@
         <v>13.2</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>25.8</v>
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2731,14 +2721,12 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>87</v>
-      </c>
+      <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
@@ -2747,7 +2735,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>2.8</v>
@@ -2766,7 +2754,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>331.8</v>
+        <v>331.3</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>23.7</v>
@@ -2775,7 +2763,7 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2783,8 +2771,8 @@
       <c r="H28" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <v>7.5</v>
+      <c r="I28" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2796,7 +2784,7 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
@@ -2817,10 +2805,10 @@
         <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2854,17 +2842,15 @@
         <v>309.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>19.7</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
@@ -2878,7 +2864,7 @@
         <v>0.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>15</v>
@@ -2893,7 +2879,7 @@
         <v>10.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="R29" s="8" t="n">
         <v>19</v>
@@ -2911,16 +2897,16 @@
         <v>13.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>79.40000000000001</v>
+        <v>1.5</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2948,7 +2934,7 @@
         <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>649.9</v>
+        <v>645.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>62.9</v>
@@ -2957,55 +2943,53 @@
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.9</v>
+        <v>69</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>412.1</v>
-      </c>
+        <v>491.8</v>
+      </c>
+      <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
-        <v>998.9</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>4135.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>85.7</v>
+        <v>8.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>829.4</v>
+        <v>824.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>6548</v>
+        <v>94228</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,8 +3010,8 @@
       <c r="D31" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E31" s="8" t="n">
-        <v>14.9</v>
+      <c r="E31" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>18.9</v>
@@ -3035,17 +3019,17 @@
       <c r="G31" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>8.1</v>
+      <c r="I31" s="8" t="n">
+        <v>81.5</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>15</v>
@@ -3055,38 +3039,36 @@
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>1454.4</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>1644.1</v>
+      </c>
+      <c r="P31" s="3" t="inlineStr"/>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>7.8</v>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>9211.6</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>8010.1</v>
+        <v>8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>19.2</v>
+        <v>16.3</v>
       </c>
       <c r="X31" s="3" t="inlineStr"/>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3105,10 +3087,10 @@
         <v>364.2</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>31.9</v>
+        <v>11.9</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>81</v>
@@ -3117,27 +3099,29 @@
         <v>14.5</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>79.3</v>
+        <v>29.1</v>
       </c>
       <c r="L32" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>12.3</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="P32" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
@@ -3145,31 +3129,31 @@
         <v>13</v>
       </c>
       <c r="R32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
         <v>14.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>1.8</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="V32" s="8" t="n">
-        <v>26.6</v>
+        <v>16.6</v>
       </c>
       <c r="W32" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>181.7</v>
+      <c r="X32" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3191,13 +3175,13 @@
         <v>23.7</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>181.7</v>
       </c>
-      <c r="G33" s="8" t="n">
-        <v>1008</v>
+      <c r="G33" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>11.5</v>
@@ -3211,14 +3195,14 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="8" t="n">
-        <v>4.9</v>
+      <c r="L33" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12.7</v>
+        <v>11.7</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>62.8</v>
+        <v>60.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3227,34 +3211,34 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>86.40000000000001</v>
+        <v>21.2</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>7.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="X33" s="8" t="n">
-        <v>87.09999999999999</v>
+      <c r="X33" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3273,16 +3257,16 @@
         <v>211.4</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>197.2</v>
+        <v>19.2</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>159.7</v>
+        <v>571.9</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>14.2</v>
@@ -3291,28 +3275,26 @@
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>98.5</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>5.2</v>
-      </c>
+        <v>15.7</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="3" t="n">
-        <v>91.8</v>
+        <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Q34" s="8" t="n">
-        <v>96.90000000000001</v>
+      <c r="Q34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
@@ -3321,22 +3303,22 @@
         <v>1.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>86.59999999999999</v>
+      <c r="X34" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3355,18 +3337,18 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
+        <v>172.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>22.2</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="G35" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="H35" s="8" t="n">
@@ -3376,7 +3358,7 @@
         <v>2.3</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0.1</v>
@@ -3387,23 +3369,21 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.4</v>
+        <v>9.4</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>29.9</v>
+        <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>17.9</v>
+        <v>18.3</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>68.8</v>
@@ -3411,14 +3391,14 @@
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>18.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>81</v>
@@ -3443,22 +3423,22 @@
         <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>713.8</v>
+        <v>25.1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>99.5</v>
+        <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>105.9</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>93.5</v>
+        <v>3.3</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4.8</v>
@@ -3467,22 +3447,22 @@
         <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>16.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>870.8</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3491,22 +3471,22 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>31.1</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V36" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1</v>
@@ -3543,28 +3523,28 @@
         <v>56.1</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>819.4</v>
+        <v>181.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>112.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>5071.7</v>
+        <v>50.7</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>62.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
@@ -3573,13 +3553,13 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3801.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>93.2</v>
+        <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>90</v>
@@ -3591,10 +3571,10 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.9</v>
+        <v>422.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3610,31 +3590,31 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>495.6</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>23.7</v>
+        <v>415.6</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>83.7</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>84.90000000000001</v>
+      <c r="F38" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>25.1</v>
+        <v>35.1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>61.5</v>
+        <v>66.5</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>17</v>
+        <v>170.2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>13.7</v>
@@ -3646,28 +3626,28 @@
         <v>41.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="8" t="n">
-        <v>117</v>
+      <c r="R38" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>2.6</v>
+        <v>16.1</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>18</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>16.3</v>
@@ -3676,10 +3656,10 @@
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>81.2</v>
+        <v>9.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3695,13 +3675,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>664.1</v>
+        <v>624.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3719,49 +3699,49 @@
         <v>5.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>69.8</v>
+      <c r="Q39" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="S39" s="8" t="n">
-        <v>521</v>
+      <c r="S39" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>27.5</v>
+        <v>26</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="8" t="n">
         <v>62.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3794,7 +3774,9 @@
       <c r="G40" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
@@ -3804,11 +3786,11 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12</v>
@@ -3817,16 +3799,16 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>48.9</v>
@@ -3835,7 +3817,7 @@
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>20.3</v>
+        <v>25.3</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>17.3</v>
@@ -3847,7 +3829,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3863,40 +3845,38 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>694.3</v>
-      </c>
-      <c r="D41" s="8" t="n">
+        <v>699.3</v>
+      </c>
+      <c r="D41" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>18.1</v>
+      <c r="E41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
         <v>4.7</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>5.3</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>98</v>
@@ -3904,35 +3884,35 @@
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>293.5</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>18.2</v>
+      <c r="Q41" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="R41" s="8" t="n">
+        <v>72.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>58.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="W41" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>641.7</v>
+      </c>
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28.8</v>
+        <v>1.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>28.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3948,49 +3928,49 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>208.8</v>
+        <v>608.8</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>181.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>53.8</v>
+        <v>3.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
-        <v>11.9</v>
+      <c r="L42" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>18.1</v>
+        <v>13.1</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>26.7</v>
+      <c r="Q42" s="8" t="n">
+        <v>61.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
@@ -4001,8 +3981,8 @@
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="U42" s="8" t="n">
-        <v>47.4</v>
+      <c r="U42" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
@@ -4011,13 +3991,13 @@
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>28.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4033,7 +4013,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>609.4</v>
+        <v>5049.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>26.1</v>
@@ -4043,7 +4023,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="n">
-        <v>1627.9</v>
+        <v>127.9</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4061,16 +4041,16 @@
         <v>13</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>1021.9</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>52.1</v>
+        <v>122.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>97</v>
+        <v>972</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
@@ -4082,25 +4062,25 @@
         <v>16.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>68</v>
+      <c r="W43" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>15.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>211.9</v>
+        <v>210.9</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4161,10 +4141,10 @@
         <v>131.9</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>23.6</v>
+        <v>53.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>77.5</v>
@@ -4176,13 +4156,13 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>27.2</v>
+        <v>127.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>56.4</v>
+        <v>36.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>55.9</v>
@@ -4191,10 +4171,10 @@
         <v>61.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>298</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4203,28 +4183,28 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>212.5</v>
+        <v>2172.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>79.8</v>
+        <v>7.6</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>83.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>658</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>382.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>281.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4246,16 +4226,16 @@
         <v>26.2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>181.5</v>
+        <v>81.5</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>200.4</v>
+        <v>1015.4</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>3.8</v>
@@ -4263,20 +4243,20 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>1111</v>
+      <c r="K46" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>1219.8</v>
+        <v>1213.8</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>111.9</v>
+        <v>101.9</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>35.1</v>
+        <v>32.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>900.1</v>
+        <v>9</v>
       </c>
       <c r="P46" s="8" t="n">
         <v>24.1</v>
@@ -4285,7 +4265,7 @@
         <v>25.3</v>
       </c>
       <c r="R46" s="8" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>1.6</v>
@@ -4294,20 +4274,20 @@
         <v>59.8</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>865.4</v>
+        <v>365.4</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>1541.6</v>
+        <v>1841.6</v>
       </c>
       <c r="W46" s="3" t="inlineStr"/>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>69.2</v>
+        <v>21.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>181.4</v>
+        <v>18.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -744,14 +744,14 @@
       <c r="E4" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>11</v>
@@ -769,15 +769,15 @@
         <v>1.5</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="R4" s="3" t="n">
@@ -787,12 +787,12 @@
         <v>19.5</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -805,7 +805,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>14649.5</v>
+        <v>464.5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>14</v>
@@ -857,19 +857,19 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -880,17 +880,17 @@
       <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>17.9</v>
+      <c r="W5" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -909,22 +909,22 @@
         <v>338</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H6" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>1.7</v>
@@ -933,13 +933,13 @@
         <v>8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>256.1</v>
+        <v>14.3</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
@@ -952,7 +952,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>62.5</v>
@@ -967,13 +967,13 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>93</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>1.3</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>353.7</v>
+        <v>355.7</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>25.3</v>
@@ -1025,7 +1025,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>8.4</v>
@@ -1034,31 +1034,31 @@
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>7.7</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>18.3</v>
+        <v>15.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.5</v>
+        <v>33.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>9</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1107,10 +1107,10 @@
         <v>13.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>12.1</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>4.1</v>
+        <v>9.9</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>8.199999999999999</v>
@@ -1125,7 +1125,7 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
@@ -1159,13 +1159,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
+        <v>182.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>126.5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>71.3</v>
+        <v>71.5</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>99</v>
@@ -1179,7 +1179,9 @@
       <c r="I9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="n">
+        <v>91.7</v>
+      </c>
       <c r="K9" s="3" t="n">
         <v>28.9</v>
       </c>
@@ -1187,16 +1189,16 @@
         <v>74.90000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>422</v>
+        <v>95.3</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>103.3</v>
@@ -1205,28 +1207,28 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>9285.6</v>
+        <v>198.6</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.1</v>
+        <v>891.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>871.2</v>
+        <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429.799999999999</v>
+        <v>9429</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>116.9</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1242,7 +1244,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3650.1</v>
+        <v>365</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>25.3</v>
@@ -1254,7 +1256,7 @@
         <v>19.8</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.3</v>
@@ -1266,25 +1268,25 @@
         <v>11.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.2</v>
+        <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.6</v>
+        <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>6.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2</v>
+        <v>20.7</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>18</v>
@@ -1293,13 +1295,13 @@
         <v>19.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>19.1</v>
+        <v>5.4</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>191.4</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17.4</v>
@@ -1327,16 +1329,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>329.6</v>
+        <v>324.6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13.3</v>
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>55.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1348,22 +1350,22 @@
         <v>0.8</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>11.8</v>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>122.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>231.6</v>
+        <v>3.9</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>91.8</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.2</v>
@@ -1374,29 +1376,29 @@
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>89.90000000000001</v>
+      <c r="S11" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>72</v>
+        <v>1220.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7.4</v>
+        <v>17.4</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>188.6</v>
+        <v>158.6</v>
       </c>
       <c r="W11" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>18.4</v>
-      </c>
       <c r="Y11" s="3" t="n">
-        <v>98.8</v>
+        <v>93.8</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1412,56 +1414,58 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>501.1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>51.7</v>
+        <v>511.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>25.7</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>110</v>
+      <c r="H12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>14.5</v>
+        <v>19.3</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>14.9</v>
+        <v>24.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.2</v>
+        <v>16.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>2.5</v>
+        <v>17.2</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>12.9</v>
+        <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1476,10 +1480,10 @@
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>89</v>
+        <v>281</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1495,19 +1499,19 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>155.6</v>
+        <v>455.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>26.8</v>
+      <c r="E13" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1519,34 +1523,34 @@
         <v>2.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>1.4</v>
+        <v>98.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>29.7</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>66.8</v>
+        <v>1866.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1561,7 +1565,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26</v>
+        <v>726</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1580,7 +1584,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.9</v>
+        <v>331.9</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>26.8</v>
@@ -1589,9 +1593,9 @@
         <v>12.3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="G14" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1606,20 +1610,20 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>94.3</v>
+        <v>12.7</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1631,22 +1635,22 @@
         <v>19.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>171.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>86.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>84</v>
+        <v>8.4</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1665,7 +1669,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>454.5</v>
+        <v>484.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>26.7</v>
@@ -1677,19 +1681,19 @@
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>13.6</v>
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.2</v>
+        <v>10.9</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>14.9</v>
@@ -1698,10 +1702,10 @@
         <v>14.9</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>18.8</v>
+        <v>1.5</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1716,7 +1720,7 @@
         <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>17.2</v>
@@ -1728,13 +1732,13 @@
         <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>84.8</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>31.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1756,13 +1760,13 @@
         <v>127.2</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>655.3</v>
+        <v>65.2</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1771,28 +1775,26 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>134.9</v>
+        <v>13.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>66.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.8</v>
+        <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>493</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>118.7</v>
+        <v>115.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>92.90000000000001</v>
@@ -1804,19 +1806,19 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>55.8</v>
+        <v>255.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>100.9</v>
+        <v>100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>190.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9421</v>
+        <v>921</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>118.4</v>
@@ -1835,19 +1837,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>814.1</v>
+        <v>461.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E17" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>12.4</v>
+        <v>112.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1856,13 +1858,13 @@
         <v>1.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
@@ -1871,7 +1873,7 @@
         <v>18.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>28.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.3</v>
@@ -1880,7 +1882,7 @@
         <v>23.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>11.8</v>
+        <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>18.3</v>
@@ -1888,11 +1890,11 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>20.1</v>
+      <c r="U17" s="8" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
@@ -1904,7 +1906,7 @@
         <v>84.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1920,10 +1922,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>955.7</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>20.9</v>
+        <v>355.7</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>22.8</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>14.3</v>
@@ -1934,12 +1936,14 @@
       <c r="G18" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="J18" s="3" t="n">
-        <v>25.3</v>
+        <v>2.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.3</v>
@@ -1947,20 +1951,20 @@
       <c r="L18" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>18</v>
+      <c r="M18" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.6</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>982.8</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>216.8</v>
+        <v>10.4</v>
       </c>
       <c r="R18" s="8" t="n">
         <v>19</v>
@@ -1969,13 +1973,13 @@
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>10.2</v>
+        <v>1</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>16.7</v>
@@ -2009,64 +2013,64 @@
         <v>25.7</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H19" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>21.8</v>
+      <c r="M19" s="8" t="n">
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.8</v>
+        <v>47</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>12.4</v>
+      <c r="S19" s="8" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>23.4</v>
+      <c r="U19" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="X19" s="8" t="n">
-        <v>88.90000000000001</v>
+      <c r="X19" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>84</v>
@@ -2088,13 +2092,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1497.9</v>
+        <v>1417.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>12.9</v>
+      <c r="E20" s="8" t="n">
+        <v>125.4</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>19.8</v>
@@ -2120,15 +2124,17 @@
       <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>184.4</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="8" t="n">
-        <v>23.9</v>
+      <c r="Q20" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
@@ -2137,25 +2143,25 @@
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2171,40 +2177,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>371.3</v>
+        <v>379.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <v>15.6</v>
+      <c r="G21" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>21.1</v>
+      <c r="K21" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>88.7</v>
+      <c r="M21" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
@@ -2216,7 +2222,7 @@
         <v>20.7</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>19.3</v>
@@ -2225,21 +2231,23 @@
         <v>80.90000000000001</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>16.9</v>
+      <c r="W21" s="8" t="n">
+        <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>918.1</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2260,13 +2268,13 @@
         <v>25.8</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>13.2</v>
+        <v>113.2</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>29.3</v>
+        <v>19.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.7</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>10.6</v>
@@ -2283,32 +2291,32 @@
       <c r="L22" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>120.9</v>
+      <c r="M22" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97</v>
+        <v>297</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q22" s="8" t="n">
-        <v>224.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>185.4</v>
+        <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.5</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>8.9</v>
+        <v>59.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2317,7 +2325,7 @@
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>92</v>
@@ -2342,7 +2350,7 @@
         <v>2089.4</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1128.4</v>
+        <v>128.2</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>66.8</v>
@@ -2351,45 +2359,47 @@
         <v>97.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>53.9</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.9</v>
+        <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>27.9</v>
+        <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>20.7</v>
+        <v>80.7</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>71.8</v>
+        <v>7.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="Q23" s="3" t="n">
         <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>918.5</v>
+        <v>191.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>3260.6</v>
+        <v>232.8</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>49.8</v>
+        <v>149.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
@@ -2398,13 +2408,13 @@
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>93.8</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>429.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>198.3</v>
+        <v>116.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2420,44 +2430,44 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4912.9</v>
+        <v>417.9</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>35.6</v>
+        <v>23.6</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>10.5</v>
+        <v>22.4</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>37.1</v>
+        <v>13.7</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>1.4</v>
+        <v>14.7</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P24" s="8" t="n">
-        <v>94.40000000000001</v>
+      <c r="P24" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>23.1</v>
@@ -2469,25 +2479,25 @@
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2503,49 +2513,49 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>223.6</v>
+        <v>233.6</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>21.8</v>
+        <v>13.3</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.6</v>
+        <v>7.6</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>8.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>16.2</v>
+        <v>8.6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.2</v>
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.5</v>
+        <v>18.8</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2557,22 +2567,22 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>71.90000000000001</v>
+        <v>27.9</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0.1</v>
+        <v>17</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>12.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>920.8</v>
+        <v>92</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>12.8</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2588,7 +2598,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>268.3</v>
+        <v>228.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
@@ -2600,15 +2610,17 @@
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K26" s="3" t="n">
         <v>17.7</v>
       </c>
@@ -2619,25 +2631,25 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2.2</v>
+        <v>18.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>908.8</v>
+        <v>108</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>18.4</v>
+        <v>81</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="S26" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S26" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2645,18 +2657,14 @@
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="Z26" s="3" t="inlineStr"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2671,7 +2679,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.8</v>
+        <v>435.6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.5</v>
@@ -2683,13 +2691,13 @@
         <v>18.9</v>
       </c>
       <c r="G27" s="8" t="n">
-        <v>131.2</v>
+        <v>12.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.7</v>
+        <v>11.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2698,13 +2706,13 @@
         <v>13.2</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>13.5</v>
+        <v>73.5</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>15.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2712,7 +2720,7 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R27" s="3" t="n">
@@ -2721,11 +2729,13 @@
       <c r="S27" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="8" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
@@ -2763,7 +2773,7 @@
         <v>13.8</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.8</v>
+        <v>18.7</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>9.9</v>
@@ -2772,7 +2782,7 @@
         <v>11.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0.3</v>
@@ -2784,13 +2794,13 @@
         <v>14.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
@@ -2802,13 +2812,13 @@
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1.8</v>
+        <v>48.1</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
@@ -2839,19 +2849,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.1</v>
+        <v>309.7</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H29" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2863,20 +2875,20 @@
       <c r="K29" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L29" s="3" t="n">
-        <v>3.7</v>
+      <c r="L29" s="8" t="n">
+        <v>13.7</v>
       </c>
       <c r="M29" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.6</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>23.6</v>
@@ -2885,22 +2897,22 @@
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.4</v>
+        <v>1.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>13.8</v>
+      <c r="V29" s="8" t="n">
+        <v>35.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>17.9</v>
+        <v>15.5</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>9.699999999999999</v>
@@ -2922,7 +2934,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1569.9</v>
+        <v>15.6</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>116.8</v>
@@ -2934,31 +2946,31 @@
         <v>94.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>645.9</v>
+        <v>44.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>62.9</v>
+        <v>62.4</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>26.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>69</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>491.8</v>
+        <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
@@ -2968,7 +2980,7 @@
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -2980,16 +2992,16 @@
         <v>8.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>824.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>94228</v>
+        <v>9428</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3008,9 +3020,9 @@
         <v>314</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E31" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="F31" s="8" t="n">
@@ -3022,53 +3034,57 @@
       <c r="H31" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>81.5</v>
+      <c r="I31" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>15</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O31" s="3" t="n">
-        <v>1644.1</v>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
+        <v>60.4</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.8</v>
+      <c r="R31" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>9211.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v>8</v>
+        <v>1.1</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="X31" s="3" t="inlineStr"/>
+      <c r="X31" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="Y31" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.1</v>
+        <v>16.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3086,38 +3102,38 @@
       <c r="C32" s="3" t="n">
         <v>364.2</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>20.9</v>
+      <c r="D32" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>11.9</v>
+        <v>19.4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>81</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>29.1</v>
+        <v>39.1</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>11.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>27.5</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>9</v>
@@ -3126,20 +3142,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>14.8</v>
-      </c>
+        <v>19.5</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="U32" s="3" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="8" t="n">
         <v>16.6</v>
       </c>
@@ -3147,13 +3159,13 @@
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>18.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3178,7 +3190,7 @@
         <v>13.7</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>181.7</v>
+        <v>81.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
@@ -3187,22 +3199,22 @@
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>11.7</v>
+        <v>17.2</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>60.1</v>
+        <v>9161.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3217,28 +3229,28 @@
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>19.6</v>
+        <v>1.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>7.8</v>
+        <v>71.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>2880.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.1</v>
+        <v>12.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3256,54 +3268,56 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>571.9</v>
+      <c r="D34" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="M34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="n">
+        <v>5.1</v>
+      </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>19.6</v>
+        <v>16.7</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>1.7</v>
+        <v>97.5</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
@@ -3311,14 +3325,14 @@
       <c r="V34" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>8</v>
@@ -3337,12 +3351,12 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>172.8</v>
+        <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E35" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="F35" s="8" t="n">
@@ -3351,7 +3365,7 @@
       <c r="G35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3366,45 +3380,47 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>14.1</v>
+      </c>
       <c r="O35" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q35" s="8" t="n">
         <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="S35" s="8" t="n">
-        <v>15.9</v>
+      <c r="S35" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>68.8</v>
+        <v>60.8</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1.7</v>
+        <v>17.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8.4</v>
+        <v>128.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3425,17 +3441,17 @@
       <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3446,23 +3462,23 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="n">
+      <c r="L36" s="3" t="n">
         <v>15</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>66.40000000000001</v>
+        <v>14.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>870.8</v>
+        <v>87</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>24</v>
+      <c r="Q36" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3471,10 +3487,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3486,10 +3502,10 @@
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>26.8</v>
+        <v>114.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3508,61 +3524,61 @@
         <v>2078.2</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1118.4</v>
+        <v>118.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>92.2</v>
+        <v>292.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.3</v>
+        <v>352.3</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>181.4</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>112.1</v>
+        <v>12.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>50.7</v>
+        <v>507.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>18.1</v>
+        <v>11.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12.6</v>
+        <v>18.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3801.9</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>81.59999999999999</v>
@@ -3571,11 +3587,9 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>422.2</v>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v>19.6</v>
-      </c>
+        <v>429.8</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3593,7 +3607,7 @@
         <v>415.6</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>83.7</v>
+        <v>23.7</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>13.2</v>
@@ -3601,65 +3615,65 @@
       <c r="F38" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>35.1</v>
+      <c r="G38" s="3" t="n">
+        <v>10.5</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>66.5</v>
+        <v>11.3</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>170.2</v>
+        <v>17</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.4</v>
+        <v>12.9</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>41.4</v>
+        <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S38" s="8" t="n">
+      <c r="R38" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>76.2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="3" t="n">
+      <c r="X38" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3675,13 +3689,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.4</v>
+        <v>624.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <v>11.1</v>
+      <c r="E39" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3693,22 +3707,22 @@
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>1.2</v>
+      <c r="L39" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="M39" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
@@ -3717,13 +3731,13 @@
         <v>1.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>14.8</v>
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3731,20 +3745,20 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W39" s="8" t="n">
-        <v>62.5</v>
+      <c r="V39" s="8" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3766,16 +3780,16 @@
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>11.6</v>
+      <c r="G40" s="8" t="n">
+        <v>65.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.3</v>
+        <v>15.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
@@ -3799,7 +3813,7 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.4</v>
@@ -3808,16 +3822,16 @@
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48.9</v>
+        <v>1948.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>25.3</v>
+        <v>22.3</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>17.3</v>
@@ -3829,7 +3843,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3845,41 +3859,39 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>699.3</v>
+        <v>644.3</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>87.09999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>1.2</v>
+      <c r="L41" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M41" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3887,32 +3899,32 @@
       <c r="Q41" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>72.2</v>
+      <c r="R41" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>97</v>
+        <v>947</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>641.7</v>
-      </c>
-      <c r="W41" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>1.5</v>
+      <c r="X41" s="8" t="n">
+        <v>88.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>22.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3933,71 +3945,69 @@
       <c r="D42" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>10.4</v>
+      <c r="E42" s="8" t="n">
+        <v>70.90000000000001</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>181.7</v>
+        <v>81.7</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.1</v>
+        <v>11.4</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="8" t="n">
-        <v>61.7</v>
+      <c r="Q42" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="n">
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>17.4</v>
+        <v>14.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4013,17 +4023,19 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>5049.4</v>
+        <v>604.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
+      <c r="F43" s="8" t="n">
+        <v>19.3</v>
+      </c>
       <c r="G43" s="3" t="n">
-        <v>127.9</v>
+        <v>13.7</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>8</v>
@@ -4037,20 +4049,20 @@
       <c r="K43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L43" s="8" t="n">
-        <v>13</v>
+      <c r="L43" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>122.7</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>972</v>
+        <v>92</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.8</v>
@@ -4059,28 +4071,28 @@
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>16.5</v>
+        <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>28.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>12.1</v>
+      <c r="X43" s="8" t="n">
+        <v>120.9</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>39.8</v>
+        <v>239.2</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>210.9</v>
+        <v>113</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4138,7 +4150,7 @@
         <v>3119.5</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>131.9</v>
+        <v>131.1</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>53.6</v>
@@ -4147,7 +4159,7 @@
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>32.9</v>
@@ -4156,25 +4168,25 @@
         <v>181.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>127.2</v>
+        <v>23.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>36.4</v>
+        <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>55.9</v>
+        <v>155.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>61.9</v>
+        <v>161.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>298</v>
+        <v>9498</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4183,25 +4195,25 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>88</v>
+        <v>81.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2172.5</v>
+        <v>282.5</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>7.6</v>
+        <v>79.8</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>108.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>10688.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>302.8</v>
+        <v>2302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4226,13 +4238,13 @@
         <v>26.2</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>101.4</v>
+        <v>101.7</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>81.5</v>
+        <v>18.5</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>1015.4</v>
+        <v>51.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4241,53 +4253,55 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.6</v>
+        <v>15.5</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>1111.9</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>1213.8</v>
+        <v>11.3</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="N46" s="8" t="n">
-        <v>32.1</v>
+        <v>11.1</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P46" s="8" t="n">
-        <v>24.1</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>12.8</v>
+      <c r="R46" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.6</v>
+        <v>11.9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>59.8</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>365.4</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>1841.6</v>
-      </c>
-      <c r="W46" s="3" t="inlineStr"/>
+        <v>65.40000000000001</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>16.6</v>
+      </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>21.8</v>
+        <v>161.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -741,20 +741,20 @@
       <c r="D4" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>10.8</v>
+      <c r="H4" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -762,23 +762,23 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>19.7</v>
+        <v>17.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>17.3</v>
@@ -792,7 +792,7 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -805,7 +805,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       <c r="G5" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -857,19 +857,19 @@
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -880,7 +880,7 @@
       <c r="V5" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -890,7 +890,7 @@
         <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -914,13 +914,13 @@
       <c r="E6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H6" s="8" t="n">
+      <c r="G6" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
@@ -930,13 +930,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>94.2</v>
+      <c r="M6" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>16.1</v>
@@ -952,10 +952,10 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>22.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
@@ -967,7 +967,7 @@
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29</v>
+        <v>20.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>76</v>
@@ -1025,16 +1025,16 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>12.2</v>
+        <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
@@ -1045,20 +1045,20 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1082,11 +1082,11 @@
       <c r="E8" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1095,7 +1095,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1103,8 +1103,8 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>13.1</v>
+      <c r="M8" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>17.1</v>
@@ -1113,10 +1113,10 @@
         <v>9.9</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.6</v>
@@ -1125,7 +1125,7 @@
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182.5</v>
+        <v>1825.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>126.5</v>
@@ -1180,7 +1180,7 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>91.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>28.9</v>
@@ -1192,10 +1192,10 @@
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.3</v>
+        <v>93</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
@@ -1207,16 +1207,16 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>198.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.8</v>
+        <v>895.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>87.2</v>
@@ -1225,7 +1225,7 @@
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1265,10 +1265,10 @@
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1100.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
@@ -1300,8 +1300,8 @@
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="8" t="n">
-        <v>191.4</v>
+      <c r="V10" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17.4</v>
@@ -1335,10 +1335,10 @@
         <v>23.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>55.3</v>
+        <v>23.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.1</v>
@@ -1352,17 +1352,17 @@
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="L11" s="8" t="n">
-        <v>122.8</v>
+      <c r="L11" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>99</v>
@@ -1370,35 +1370,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>2.3</v>
+      <c r="Q11" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1220.4</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>158.6</v>
-      </c>
-      <c r="W11" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>18.9</v>
+        <v>26.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>11.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>25.7</v>
@@ -1432,28 +1432,28 @@
         <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>24.4</v>
+      <c r="L12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
@@ -1473,17 +1473,17 @@
       <c r="V12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       <c r="D13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="F13" s="3" t="n">
@@ -1517,7 +1517,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1526,19 +1526,19 @@
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>98.2</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1550,7 +1550,7 @@
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1866.8</v>
+        <v>66.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1565,7 +1565,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>726</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>331.9</v>
+        <v>531.1</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>26.8</v>
@@ -1592,7 +1592,7 @@
       <c r="E14" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1602,7 +1602,7 @@
         <v>8.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>3.6</v>
@@ -1617,13 +1617,13 @@
         <v>12.7</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.6</v>
@@ -1647,10 +1647,10 @@
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1675,7 +1675,7 @@
         <v>26.7</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>20.4</v>
@@ -1687,10 +1687,10 @@
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1.6</v>
@@ -1698,14 +1698,14 @@
       <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>14.9</v>
+      <c r="M15" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
@@ -1735,7 +1735,7 @@
         <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2306.9</v>
+        <v>230.6</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>127.2</v>
@@ -1766,7 +1766,7 @@
         <v>95.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1775,7 +1775,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>19.6</v>
@@ -1790,38 +1790,38 @@
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>432</v>
+        <v>95</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
-        <v>115.7</v>
+        <v>118.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>313</v>
+        <v>13</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>255.8</v>
+        <v>55.8</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>100.4</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>190.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>24</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>461.4</v>
+        <v>51.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>112.4</v>
+      <c r="G17" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1860,11 +1860,11 @@
       <c r="J17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>13.9</v>
+      <c r="K17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>13.2</v>
@@ -1890,11 +1890,11 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="8" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>1.4</v>
+      <c r="U17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>18.2</v>
@@ -1924,13 +1924,13 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E18" s="8" t="n">
+      <c r="D18" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="G18" s="3" t="n">
@@ -1949,13 +1949,13 @@
         <v>0.3</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>19.2</v>
+        <v>14.2</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>98</v>
@@ -1963,20 +1963,20 @@
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="R18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R18" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>20.2</v>
@@ -2007,40 +2007,40 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
+        <v>235.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>11.8</v>
+      <c r="M19" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2049,13 +2049,13 @@
         <v>0.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="8" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
@@ -2063,7 +2063,7 @@
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2092,15 +2092,15 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1417.9</v>
+        <v>17.9</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>125.4</v>
-      </c>
-      <c r="F20" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G20" s="3" t="n">
@@ -2125,7 +2125,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2134,7 +2134,7 @@
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>17.5</v>
@@ -2143,13 +2143,13 @@
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>12.2</v>
+        <v>19.2</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>17.7</v>
@@ -2158,7 +2158,7 @@
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.9</v>
@@ -2177,15 +2177,15 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
+        <v>371.3</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E21" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="G21" s="3" t="n">
@@ -2198,10 +2198,10 @@
         <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K21" s="8" t="n">
-        <v>41.1</v>
+        <v>2.1</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>16.5</v>
@@ -2210,13 +2210,13 @@
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>20.7</v>
@@ -2236,17 +2236,17 @@
       <c r="V21" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>918.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
       <c r="D22" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="F22" s="8" t="n">
+      <c r="E22" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2286,19 +2286,19 @@
         <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>51.7</v>
+        <v>5.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.6</v>
@@ -2310,13 +2310,13 @@
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>18.9</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2089.4</v>
+        <v>208.9</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>128.2</v>
@@ -2374,7 +2374,7 @@
         <v>27.4</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>80.7</v>
+        <v>70.7</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>69.59999999999999</v>
@@ -2386,20 +2386,20 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>115.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>191.5</v>
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>232.8</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
+        <v>49.8</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>94.3</v>
@@ -2411,10 +2411,10 @@
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2430,34 +2430,36 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>417.9</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E24" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H24" s="8" t="n">
+      <c r="G24" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2479,12 +2481,12 @@
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>15.4</v>
+        <v>25.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="8" t="n">
+      <c r="V24" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W24" s="3" t="n">
@@ -2513,13 +2515,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>233.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>13.3</v>
+        <v>15.5</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>19.3</v>
@@ -2527,7 +2529,7 @@
       <c r="G25" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
@@ -2537,13 +2539,13 @@
         <v>0.8</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>16</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>19.8</v>
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>18.8</v>
@@ -2555,7 +2557,7 @@
         <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>17.2</v>
@@ -2567,10 +2569,10 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>27.9</v>
+        <v>2.4</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2579,7 +2581,7 @@
         <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>1</v>
@@ -2598,7 +2600,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>228.3</v>
+        <v>268.3</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>22.4</v>
@@ -2613,7 +2615,7 @@
         <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
@@ -2627,29 +2629,29 @@
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.2</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>18</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S26" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2679,7 +2681,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>435.6</v>
+        <v>35.6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.5</v>
@@ -2690,14 +2692,14 @@
       <c r="F27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>12.2</v>
+      <c r="G27" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
@@ -2705,14 +2707,14 @@
       <c r="K27" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>73.5</v>
+      <c r="L27" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>15.4</v>
+        <v>13.4</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2727,22 +2729,22 @@
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="8" t="n">
+      <c r="V27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2785,7 +2787,7 @@
         <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>32.8</v>
@@ -2797,10 +2799,10 @@
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
@@ -2808,22 +2810,22 @@
       <c r="Q28" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>48.1</v>
+        <v>78</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2849,10 +2851,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.7</v>
+        <v>309.1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>14</v>
@@ -2863,7 +2865,7 @@
       <c r="G29" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2873,19 +2875,19 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.2</v>
@@ -2893,29 +2895,29 @@
       <c r="Q29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.1</v>
+        <v>19.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>6.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="8" t="n">
-        <v>35.8</v>
+      <c r="V29" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2934,7 +2936,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.6</v>
+        <v>156.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>116.8</v>
@@ -2967,29 +2969,29 @@
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
       <c r="Q30" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>413.1</v>
+        <v>13.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>8.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>82.40000000000001</v>
@@ -2998,10 +3000,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9428</v>
+        <v>475</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3019,17 +3021,17 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3041,35 +3043,35 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>60.4</v>
+        <v>22.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
+        <v>20.1</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>87.8</v>
+      <c r="R31" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>17</v>
@@ -3084,7 +3086,7 @@
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3100,72 +3102,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D32" s="8" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="D32" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="E32" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="E32" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>71.59999999999999</v>
+        <v>39.3</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>19.5</v>
+      <c r="R32" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3181,21 +3183,21 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>411.2</v>
+        <v>11.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="3" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>81.7</v>
+      <c r="F33" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
@@ -3208,13 +3210,13 @@
         <v>7.2</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="8" t="n">
-        <v>9161.9</v>
+      <c r="N33" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3229,28 +3231,28 @@
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2880.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3278,7 +3280,7 @@
         <v>17.4</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14.2</v>
@@ -3290,13 +3292,13 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>5.1</v>
+        <v>115</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
@@ -3305,37 +3307,37 @@
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>97.5</v>
+        <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W34" s="8" t="n">
+      <c r="V34" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3351,15 +3353,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>477.8</v>
+        <v>77.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3380,7 +3382,7 @@
       <c r="L35" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3392,25 +3394,25 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
+        <v>8.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="W35" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W35" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3420,7 +3422,7 @@
         <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>128.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3436,12 +3438,12 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>613.2</v>
+        <v>13.2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F36" s="3" t="n">
@@ -3451,7 +3453,7 @@
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3472,13 +3474,13 @@
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>21</v>
+      <c r="Q36" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3487,10 +3489,10 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.1</v>
+        <v>52.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.8</v>
@@ -3502,10 +3504,10 @@
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>114.8</v>
+        <v>71.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3523,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2078.2</v>
+        <v>20.7</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>118.4</v>
@@ -3530,46 +3532,46 @@
         <v>66.09999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>292.2</v>
+        <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>352.3</v>
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>507.9</v>
+        <v>50.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>59.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>380.9</v>
@@ -3587,7 +3589,7 @@
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.8</v>
+        <v>429.5</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3604,12 +3606,12 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>415.6</v>
+        <v>15.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="F38" s="3" t="n">
@@ -3618,19 +3620,19 @@
       <c r="G38" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I38" s="8" t="n">
-        <v>17</v>
+      <c r="I38" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M38" s="3" t="n">
@@ -3640,16 +3642,16 @@
         <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>8.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="8" t="n">
-        <v>97</v>
+      <c r="R38" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17.6</v>
@@ -3666,11 +3668,11 @@
       <c r="W38" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>3.1</v>
@@ -3689,13 +3691,13 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>624.3</v>
+        <v>24.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.5</v>
@@ -3707,7 +3709,7 @@
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.3</v>
@@ -3715,26 +3717,26 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
+      <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>0.1</v>
@@ -3745,11 +3747,11 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="8" t="n">
-        <v>71.5</v>
+      <c r="V39" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>16.5</v>
@@ -3774,28 +3776,28 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>637.7</v>
+        <v>37.7</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <v>65.3</v>
+      <c r="G40" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3813,7 +3815,7 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.4</v>
@@ -3825,7 +3827,7 @@
         <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
@@ -3865,7 +3867,7 @@
         <v>26.2</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3876,22 +3878,22 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3903,10 +3905,10 @@
         <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.1</v>
+        <v>22.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>947</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
@@ -3917,11 +3919,11 @@
       <c r="W41" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="8" t="n">
-        <v>88.8</v>
+      <c r="X41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>16.8</v>
@@ -3945,11 +3947,11 @@
       <c r="D42" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <v>81.7</v>
+      <c r="E42" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>16.5</v>
@@ -3958,31 +3960,31 @@
         <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18.2</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18.2</v>
@@ -3992,16 +3994,16 @@
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>14.4</v>
+        <v>17.4</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="8" t="n">
+      <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
@@ -4031,7 +4033,7 @@
       <c r="E43" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G43" s="3" t="n">
@@ -4044,22 +4046,22 @@
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.4</v>
+        <v>5.4</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>19.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.6</v>
@@ -4077,22 +4079,22 @@
         <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>22.4</v>
+        <v>14.9</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="8" t="n">
-        <v>120.9</v>
+      <c r="X43" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>239.2</v>
+        <v>29.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4147,7 +4149,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3119.5</v>
+        <v>119.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>131.1</v>
@@ -4159,34 +4161,34 @@
         <v>92.5</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>155.9</v>
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>161.9</v>
+        <v>60.9</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>9498</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>126.3</v>
@@ -4195,10 +4197,10 @@
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>282.5</v>
+        <v>252.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
@@ -4210,10 +4212,10 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>10688.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2302.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>20.7</v>
@@ -4237,14 +4239,14 @@
       <c r="D46" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="F46" s="8" t="n">
+      <c r="E46" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>51.3</v>
+      <c r="G46" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4253,22 +4255,22 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="L46" s="8" t="n">
+        <v>11111111</v>
+      </c>
+      <c r="L46" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>1.4</v>
@@ -4280,25 +4282,25 @@
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.9</v>
+        <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>65.40000000000001</v>
+        <v>50.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>10.1</v>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -805,7 +796,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -952,10 +943,10 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>18.1</v>
+        <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.5</v>
+        <v>67.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
@@ -1025,7 +1016,7 @@
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.4</v>
@@ -1107,10 +1098,10 @@
         <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>17.1</v>
+        <v>171.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.2</v>
@@ -1195,7 +1186,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>93</v>
+        <v>493</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
@@ -1207,10 +1198,10 @@
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>895.5</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1225,7 +1216,7 @@
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1267,8 +1258,8 @@
       <c r="J10" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>1100.1</v>
+      <c r="K10" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
@@ -1280,7 +1271,7 @@
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
@@ -1310,7 +1301,7 @@
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.8</v>
+        <v>86.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1335,7 +1326,7 @@
         <v>23.4</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>15.3</v>
@@ -1356,7 +1347,7 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>15.8</v>
+        <v>11.8</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>13.7</v>
@@ -1377,7 +1368,7 @@
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>72</v>
@@ -1392,7 +1383,7 @@
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>26.4</v>
+        <v>16.4</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>95</v>
@@ -1414,7 +1405,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11.1</v>
+        <v>511.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>25.7</v>
@@ -1447,13 +1438,13 @@
         <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
@@ -1465,7 +1456,7 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1538,7 +1529,7 @@
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1565,7 +1556,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1614,10 +1605,10 @@
         <v>12.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
@@ -1681,13 +1672,13 @@
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>21.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1790,7 +1781,7 @@
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>95</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
       <c r="Q16" s="3" t="n">
@@ -1803,7 +1794,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>13</v>
+        <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>55.8</v>
@@ -1815,10 +1806,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.8</v>
+        <v>99.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>24</v>
+        <v>424</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1837,10 +1828,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>51.4</v>
+        <v>461.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13</v>
@@ -1955,10 +1946,10 @@
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
@@ -2007,7 +1998,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>235.6</v>
+        <v>2135.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
@@ -2031,16 +2022,16 @@
         <v>4.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2092,7 +2083,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>17.9</v>
+        <v>417.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>27.2</v>
@@ -2125,7 +2116,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
+        <v>19.2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2180,7 +2171,7 @@
         <v>371.3</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>14</v>
@@ -2240,10 +2231,10 @@
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>0.4</v>
@@ -2295,7 +2286,7 @@
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.8</v>
+        <v>14.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2347,7 +2338,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>208.9</v>
+        <v>2089.4</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>128.2</v>
@@ -2368,7 +2359,7 @@
         <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>27.4</v>
@@ -2411,7 +2402,7 @@
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>29</v>
+        <v>429</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>16.3</v>
@@ -2430,7 +2421,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>17.9</v>
+        <v>417.9</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>25.6</v>
@@ -2454,16 +2445,16 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2481,7 +2472,7 @@
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>25.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
@@ -2499,7 +2490,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2515,7 +2506,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.5</v>
+        <v>233.6</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
@@ -2548,7 +2539,7 @@
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2569,10 +2560,10 @@
         <v>89</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2612,7 +2603,7 @@
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>7.1</v>
+        <v>71.2</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2633,7 +2624,7 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2681,7 +2672,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>35.6</v>
+        <v>435.6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>24.5</v>
@@ -2744,7 +2735,7 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2814,10 +2805,10 @@
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>15.9</v>
+        <v>16.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>5</v>
@@ -2875,10 +2866,10 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>15</v>
@@ -2899,7 +2890,7 @@
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>66.09999999999999</v>
@@ -2911,7 +2902,7 @@
         <v>15.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>17.4</v>
@@ -2939,7 +2930,7 @@
         <v>156.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>116.8</v>
+        <v>1168.2</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>71.90000000000001</v>
@@ -2969,7 +2960,7 @@
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
@@ -2982,10 +2973,10 @@
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>13.1</v>
+        <v>413.1</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>21.8</v>
@@ -3000,7 +2991,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>5.4</v>
@@ -3022,16 +3013,16 @@
         <v>314</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>23.4</v>
+        <v>123.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>18.9</v>
+        <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3047,10 +3038,10 @@
         <v>15</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.9</v>
+        <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.1</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>22.8</v>
@@ -3068,13 +3059,13 @@
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17</v>
+        <v>170.4</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.3</v>
@@ -3105,13 +3096,13 @@
         <v>364.6</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>20.7</v>
+        <v>25.7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>18.5</v>
+        <v>1815</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
@@ -3126,19 +3117,19 @@
         <v>1.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.3</v>
+        <v>32.3</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>11.1</v>
+        <v>21.9</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3167,7 +3158,7 @@
         <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3183,7 +3174,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>11.2</v>
+        <v>411.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>23.7</v>
@@ -3237,7 +3228,7 @@
         <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>17.8</v>
@@ -3249,10 +3240,10 @@
         <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3295,16 +3286,16 @@
         <v>3.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>115</v>
+        <v>1150</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>29.1</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3319,10 +3310,10 @@
         <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>16.4</v>
@@ -3337,7 +3328,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3353,7 +3344,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>77.8</v>
+        <v>477.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>24.2</v>
@@ -3401,7 +3392,7 @@
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>8.9</v>
+        <v>27.9</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3438,7 +3429,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>13.2</v>
+        <v>613.2</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>25.1</v>
@@ -3474,7 +3465,7 @@
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3489,7 +3480,7 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
+        <v>54.1</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.4</v>
@@ -3523,7 +3514,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>20.7</v>
+        <v>207.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>118.4</v>
@@ -3535,7 +3526,7 @@
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>52.3</v>
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3562,7 +3553,7 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
@@ -3574,13 +3565,13 @@
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3809.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>81.59999999999999</v>
@@ -3606,7 +3597,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15.6</v>
+        <v>415.6</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>23.7</v>
@@ -3630,7 +3621,7 @@
         <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>13.7</v>
@@ -3691,7 +3682,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>24.3</v>
+        <v>624.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.9</v>
@@ -3727,19 +3718,19 @@
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3776,7 +3767,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>37.7</v>
+        <v>637.7</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>26</v>
@@ -3815,7 +3806,7 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.4</v>
@@ -3824,7 +3815,7 @@
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>48</v>
@@ -3867,7 +3858,7 @@
         <v>26.2</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>18.1</v>
@@ -3890,10 +3881,10 @@
         <v>10.5</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3948,7 +3939,7 @@
         <v>26.9</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>18.7</v>
@@ -4076,10 +4067,10 @@
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.8</v>
+        <v>32.2</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>14.9</v>
+        <v>18.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>21.4</v>
@@ -4149,7 +4140,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>119.5</v>
+        <v>3119.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>131.1</v>
@@ -4182,10 +4173,10 @@
         <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>60.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
@@ -4218,7 +4209,7 @@
         <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.7</v>
+        <v>50.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4257,8 +4248,8 @@
       <c r="J46" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>11111111</v>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>11.3</v>
@@ -4273,7 +4264,7 @@
         <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>25.3</v>
@@ -4285,13 +4276,13 @@
         <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>50.5</v>
+        <v>58.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>21.8</v>
+        <v>218.4</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>16.6</v>

--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_decimal_place_correction.xlsx
@@ -943,7 +943,7 @@
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>67.5</v>
@@ -1007,7 +1007,7 @@
         <v>4.8</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>15.2</v>
@@ -1034,7 +1034,7 @@
         <v>77</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>18.8</v>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>377.9</v>
+        <v>37.7</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>24.4</v>
@@ -1098,7 +1098,7 @@
         <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>171.9</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>99</v>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1825.2</v>
+        <v>182.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>126.5</v>
@@ -1201,7 +1201,7 @@
         <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2.8</v>
+        <v>89.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
@@ -1259,7 +1259,7 @@
         <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>10.1</v>
+        <v>21</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>15</v>
@@ -1271,7 +1271,7 @@
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>28.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
@@ -1301,7 +1301,7 @@
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>86.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1347,10 +1347,10 @@
         <v>17.9</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.8</v>
+        <v>15.8</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>13.7</v>
+        <v>18.7</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>15.6</v>
@@ -1383,7 +1383,7 @@
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>16.4</v>
+        <v>20.8</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>95</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>511.1</v>
+        <v>51.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>25.7</v>
@@ -1438,13 +1438,13 @@
         <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>24.3</v>
@@ -1456,7 +1456,7 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>22.2</v>
+        <v>30.1</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
@@ -1502,7 +1502,7 @@
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>8.6</v>
@@ -1529,7 +1529,7 @@
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>23.8</v>
@@ -1556,7 +1556,7 @@
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1638,7 +1638,7 @@
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>20.3</v>
+        <v>22.3</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>84</v>
@@ -1672,13 +1672,13 @@
         <v>20.4</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>12.6</v>
+        <v>22.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.2</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>230.6</v>
+        <v>230</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>127.2</v>
@@ -1806,10 +1806,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.3</v>
+        <v>99.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>18.4</v>
@@ -1831,7 +1831,7 @@
         <v>461.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13</v>
@@ -1852,7 +1852,7 @@
         <v>2.7</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.8</v>
+        <v>2</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>13.4</v>
@@ -1946,10 +1946,10 @@
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2135.6</v>
+        <v>335.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>25.7</v>
@@ -2028,7 +2028,7 @@
         <v>14.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>19.8</v>
+        <v>11.8</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>18.5</v>
@@ -2049,7 +2049,7 @@
         <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>36.1</v>
+        <v>56.1</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>13.4</v>
@@ -2116,7 +2116,7 @@
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.2</v>
+        <v>1.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2137,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>19.2</v>
@@ -2201,7 +2201,7 @@
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
@@ -2231,7 +2231,7 @@
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>98</v>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>508.9</v>
+        <v>50.8</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>25.8</v>
@@ -2286,7 +2286,7 @@
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.4</v>
+        <v>18.4</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2454,7 +2454,7 @@
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.2</v>
+        <v>1.7</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>233.6</v>
+        <v>233.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>23.1</v>
@@ -2539,7 +2539,7 @@
         <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2563,7 +2563,7 @@
         <v>2.9</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>17</v>
@@ -2603,7 +2603,7 @@
         <v>18.9</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>71.2</v>
+        <v>7.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>13.2</v>
@@ -2624,7 +2624,7 @@
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>12.2</v>
+        <v>17.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2735,7 +2735,7 @@
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2826,7 +2826,7 @@
         <v>98</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>13.1</v>
+        <v>13.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>15</v>
@@ -2930,7 +2930,7 @@
         <v>156.9</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1168.2</v>
+        <v>116.8</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>71.90000000000001</v>
@@ -2973,7 +2973,7 @@
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>413.1</v>
@@ -3013,7 +3013,7 @@
         <v>314</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>123.4</v>
+        <v>23.4</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>14.4</v>
@@ -3022,7 +3022,7 @@
         <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>12.5</v>
@@ -3041,13 +3041,13 @@
         <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>22.8</v>
+        <v>0.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>20.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>19.9</v>
@@ -3059,13 +3059,13 @@
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>170.4</v>
+        <v>170</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>16.3</v>
@@ -3096,13 +3096,13 @@
         <v>364.6</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1815</v>
+        <v>18.5</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>14.3</v>
@@ -3114,22 +3114,22 @@
         <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>32.3</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3152,13 +3152,13 @@
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>211.4</v>
+        <v>21.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>19.7</v>
@@ -3289,13 +3289,13 @@
         <v>15.1</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>1150</v>
+        <v>15</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>29.1</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3310,7 +3310,7 @@
         <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>2</v>
@@ -3328,7 +3328,7 @@
         <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.9</v>
+        <v>212.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>60</v>
@@ -3471,7 +3471,7 @@
         <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>17.6</v>
@@ -3480,7 +3480,7 @@
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>54.1</v>
+        <v>58.1</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>13.4</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>207.8</v>
+        <v>7.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>118.4</v>
@@ -3526,7 +3526,7 @@
         <v>92.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>32.3</v>
+        <v>52.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
@@ -3553,7 +3553,7 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>101</v>
@@ -3565,7 +3565,7 @@
         <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3809.1</v>
+        <v>380.9</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
@@ -3636,7 +3636,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>20.2</v>
@@ -3718,19 +3718,19 @@
         <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3815,10 +3815,10 @@
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
@@ -3836,7 +3836,7 @@
         <v>62.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
@@ -3917,7 +3917,7 @@
         <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>61</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>12.7</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>97</v>
@@ -4067,10 +4067,10 @@
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>32.2</v>
+        <v>22.8</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>18.9</v>
+        <v>14.9</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>21.4</v>
@@ -4082,7 +4082,7 @@
         <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>29.8</v>
+        <v>19.8</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>13</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
@@ -4170,13 +4170,13 @@
         <v>56.4</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>55.9</v>
+        <v>55.4</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>26</v>
+        <v>490</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>2</v>
@@ -4203,7 +4203,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>302.8</v>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>223.9</v>
+        <v>623.9</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>26.2</v>
@@ -4249,13 +4249,13 @@
         <v>5.5</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
@@ -4276,13 +4276,13 @@
         <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
+        <v>50.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>218.4</v>
+        <v>21.8</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>16.6</v>
